--- a/data/secondary/secondary_quote_2026-07-21.xlsx
+++ b/data/secondary/secondary_quote_2026-07-21.xlsx
@@ -14,60 +14,795 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
-  <si>
-    <t>暂无数据</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1680" uniqueCount="263">
+  <si>
+    <t>债券简称</t>
+  </si>
+  <si>
+    <t>债券代码</t>
+  </si>
+  <si>
+    <t>剩余期限</t>
+  </si>
+  <si>
+    <t>最新成交</t>
+  </si>
+  <si>
+    <t>开盘</t>
+  </si>
+  <si>
+    <t>最高</t>
+  </si>
+  <si>
+    <t>最低</t>
+  </si>
+  <si>
+    <t>平均成交</t>
+  </si>
+  <si>
+    <t>前收</t>
+  </si>
+  <si>
+    <t>成交笔数</t>
+  </si>
+  <si>
+    <t>GVN笔数</t>
+  </si>
+  <si>
+    <t>TKN笔数</t>
+  </si>
+  <si>
+    <t>中债(行/到)</t>
+  </si>
+  <si>
+    <t>列14</t>
+  </si>
+  <si>
+    <t>更新时间</t>
+  </si>
+  <si>
+    <t>流动性评分</t>
+  </si>
+  <si>
+    <t>中债隐含评级</t>
+  </si>
+  <si>
+    <t>中证净价</t>
+  </si>
+  <si>
+    <t>主承销商</t>
+  </si>
+  <si>
+    <t>列20</t>
+  </si>
+  <si>
+    <t>发行日</t>
+  </si>
+  <si>
+    <t>主/债</t>
+  </si>
+  <si>
+    <t>24云能投MTN015</t>
+  </si>
+  <si>
+    <t>102482996.IB</t>
+  </si>
+  <si>
+    <t>7.98Y</t>
+  </si>
+  <si>
+    <t>2.8400</t>
+  </si>
+  <si>
+    <t>--</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2.8375</t>
+  </si>
+  <si>
+    <t>0.25</t>
+  </si>
+  <si>
+    <t>02:34:47</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>**</t>
+  </si>
+  <si>
+    <t>103.4455</t>
+  </si>
+  <si>
+    <t>中国光大银行股份有限公司</t>
+  </si>
+  <si>
+    <t>2024-07-10</t>
+  </si>
+  <si>
+    <t>AAA/--</t>
+  </si>
+  <si>
+    <t>24鄂联投MTN007</t>
+  </si>
+  <si>
+    <t>102483395.IB</t>
+  </si>
+  <si>
+    <t>8.05Y</t>
+  </si>
+  <si>
+    <t>2.6500</t>
+  </si>
+  <si>
+    <t>2.6844</t>
+  </si>
+  <si>
+    <t>-3.44</t>
+  </si>
+  <si>
+    <t>06:12:19</t>
+  </si>
+  <si>
+    <t>98.6210</t>
+  </si>
+  <si>
+    <t>广发证券股份有限公司</t>
+  </si>
+  <si>
+    <t>2024-08-05</t>
+  </si>
+  <si>
+    <t>AAA/AAA</t>
+  </si>
+  <si>
+    <t>26农行二级资本债01B(BC)</t>
+  </si>
+  <si>
+    <t>232680006.IB</t>
+  </si>
+  <si>
+    <t>9.81Y+5.00Y</t>
+  </si>
+  <si>
+    <t>2.1550</t>
+  </si>
+  <si>
+    <t>2.1475</t>
+  </si>
+  <si>
+    <t>0.75</t>
+  </si>
+  <si>
+    <t>2.1535/2.2842</t>
+  </si>
+  <si>
+    <t>0.15</t>
+  </si>
+  <si>
+    <t>06:06:03</t>
+  </si>
+  <si>
+    <t>101.7820</t>
+  </si>
+  <si>
+    <t>中国国际金融股份有限公司</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>25农行二级资本债03B(BC)</t>
+  </si>
+  <si>
+    <t>232580036.IB</t>
+  </si>
+  <si>
+    <t>9.16Y+5.00Y</t>
+  </si>
+  <si>
+    <t>2.1500</t>
+  </si>
+  <si>
+    <t>2.1494</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>2.15/2.2643</t>
+  </si>
+  <si>
+    <t>-0.25</t>
+  </si>
+  <si>
+    <t>06:19:47</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>103.0271</t>
+  </si>
+  <si>
+    <t>2025-09-16</t>
+  </si>
+  <si>
+    <t>25农行二级资本债02B(BC)</t>
+  </si>
+  <si>
+    <t>232580025.IB</t>
+  </si>
+  <si>
+    <t>9.01Y+5.00Y</t>
+  </si>
+  <si>
+    <t>2.1425</t>
+  </si>
+  <si>
+    <t>2.1450</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>2.1427/2.2299</t>
+  </si>
+  <si>
+    <t>-0.02</t>
+  </si>
+  <si>
+    <t>05:21:02</t>
+  </si>
+  <si>
+    <t>100.8618</t>
+  </si>
+  <si>
+    <t>2025-07-21</t>
+  </si>
+  <si>
+    <t>25农行二级资本债01B(BC)</t>
+  </si>
+  <si>
+    <t>232580017.IB</t>
+  </si>
+  <si>
+    <t>8.91Y+5.00Y</t>
+  </si>
+  <si>
+    <t>2.1400</t>
+  </si>
+  <si>
+    <t>2.1405</t>
+  </si>
+  <si>
+    <t>0.00</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>2.1421/2.2270</t>
+  </si>
+  <si>
+    <t>-0.21</t>
+  </si>
+  <si>
+    <t>07:48:48</t>
+  </si>
+  <si>
+    <t>100.8303</t>
+  </si>
+  <si>
+    <t>2025-06-12</t>
+  </si>
+  <si>
+    <t>25成都开投MTN001A</t>
+  </si>
+  <si>
+    <t>102583788.IB</t>
+  </si>
+  <si>
+    <t>4.13Y+5.00Y</t>
+  </si>
+  <si>
+    <t>2.1300</t>
+  </si>
+  <si>
+    <t>2.1403/3.0004</t>
+  </si>
+  <si>
+    <t>-1.03</t>
+  </si>
+  <si>
+    <t>05:43:52</t>
+  </si>
+  <si>
+    <t>D+</t>
+  </si>
+  <si>
+    <t>102.7546</t>
+  </si>
+  <si>
+    <t>国信证券股份有限公司</t>
+  </si>
+  <si>
+    <t>2025-09-03</t>
+  </si>
+  <si>
+    <t>AA+/--</t>
+  </si>
+  <si>
+    <t>25北部湾银行二级资本债01</t>
+  </si>
+  <si>
+    <t>232580011.IB</t>
+  </si>
+  <si>
+    <t>3.85Y+5.00Y</t>
+  </si>
+  <si>
+    <t>2.1200</t>
+  </si>
+  <si>
+    <t>2.1331/2.7648</t>
+  </si>
+  <si>
+    <t>-1.31</t>
+  </si>
+  <si>
+    <t>05:43:07</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>103.0296</t>
+  </si>
+  <si>
+    <t>2025-05-21</t>
+  </si>
+  <si>
+    <t>AAA/AA+</t>
+  </si>
+  <si>
+    <t>24万州经开MTN008</t>
+  </si>
+  <si>
+    <t>102401119.IB</t>
+  </si>
+  <si>
+    <t>3.43Y</t>
+  </si>
+  <si>
+    <t>2.1000</t>
+  </si>
+  <si>
+    <t>2.0549</t>
+  </si>
+  <si>
+    <t>4.51</t>
+  </si>
+  <si>
+    <t>07:13:37</t>
+  </si>
+  <si>
+    <t>D-</t>
+  </si>
+  <si>
+    <t>102.9629</t>
+  </si>
+  <si>
+    <t>重庆银行股份有限公司</t>
+  </si>
+  <si>
+    <t>2024-12-22</t>
+  </si>
+  <si>
+    <t>24万州经开MTN009</t>
+  </si>
+  <si>
+    <t>102401122.IB</t>
+  </si>
+  <si>
+    <t>2.0555</t>
+  </si>
+  <si>
+    <t>4.45</t>
+  </si>
+  <si>
+    <t>07:08:09</t>
+  </si>
+  <si>
+    <t>103.6857</t>
+  </si>
+  <si>
+    <t>2024-12-23</t>
+  </si>
+  <si>
+    <t>26武汉开投PPN003</t>
+  </si>
+  <si>
+    <t>032680249.IB</t>
+  </si>
+  <si>
+    <t>2.98Y</t>
+  </si>
+  <si>
+    <t>2.0900</t>
+  </si>
+  <si>
+    <t>1.00</t>
+  </si>
+  <si>
+    <t>2.0995</t>
+  </si>
+  <si>
+    <t>0.05</t>
+  </si>
+  <si>
+    <t>03:35:01</t>
+  </si>
+  <si>
+    <t>S-</t>
+  </si>
+  <si>
+    <t>99.8233</t>
+  </si>
+  <si>
+    <t>国泰海通证券股份有限公司</t>
+  </si>
+  <si>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>24金堂现代PPN001A</t>
+  </si>
+  <si>
+    <t>032480903.IB</t>
+  </si>
+  <si>
+    <t>3.07Y</t>
+  </si>
+  <si>
+    <t>2.0800</t>
+  </si>
+  <si>
+    <t>2.0973</t>
+  </si>
+  <si>
+    <t>-1.73</t>
+  </si>
+  <si>
+    <t>02:27:58</t>
+  </si>
+  <si>
+    <t>102.6929</t>
+  </si>
+  <si>
+    <t>成都银行股份有限公司</t>
+  </si>
+  <si>
+    <t>2024-08-14</t>
+  </si>
+  <si>
+    <t>AA/AAA</t>
+  </si>
+  <si>
+    <t>24农行二级资本债02B</t>
+  </si>
+  <si>
+    <t>232480012.IB</t>
+  </si>
+  <si>
+    <t>7.76Y+5.00Y</t>
+  </si>
+  <si>
+    <t>2.0700</t>
+  </si>
+  <si>
+    <t>2.0750</t>
+  </si>
+  <si>
+    <t>2.0681/2.1932</t>
+  </si>
+  <si>
+    <t>0.19</t>
+  </si>
+  <si>
+    <t>06:19:08</t>
+  </si>
+  <si>
+    <t>103.0835</t>
+  </si>
+  <si>
+    <t>中信证券股份有限公司</t>
+  </si>
+  <si>
+    <t>2024-04-22</t>
+  </si>
+  <si>
+    <t>26武开02</t>
+  </si>
+  <si>
+    <t>134890.SZ</t>
+  </si>
+  <si>
+    <t>2.63Y</t>
+  </si>
+  <si>
+    <t>2.0600</t>
+  </si>
+  <si>
+    <t>2.0585</t>
+  </si>
+  <si>
+    <t>07:46:19</t>
+  </si>
+  <si>
+    <t>101.1224</t>
+  </si>
+  <si>
+    <t>华源证券股份有限公司</t>
+  </si>
+  <si>
+    <t>0.68</t>
+  </si>
+  <si>
+    <t>2026-03-05</t>
+  </si>
+  <si>
+    <t>AA+/AAA</t>
+  </si>
+  <si>
+    <t>24农行二级资本债01B</t>
+  </si>
+  <si>
+    <t>232480005.IB</t>
+  </si>
+  <si>
+    <t>7.55Y+5.00Y</t>
+  </si>
+  <si>
+    <t>2.0525</t>
+  </si>
+  <si>
+    <t>2.0550</t>
+  </si>
+  <si>
+    <t>2.0544</t>
+  </si>
+  <si>
+    <t>2.0500</t>
+  </si>
+  <si>
+    <t>2.0522/2.1871</t>
+  </si>
+  <si>
+    <t>0.03</t>
+  </si>
+  <si>
+    <t>06:07:20</t>
+  </si>
+  <si>
+    <t>105.1959</t>
+  </si>
+  <si>
+    <t>2024-02-01</t>
+  </si>
+  <si>
+    <t>26国耀K1</t>
+  </si>
+  <si>
+    <t>245347.SH</t>
+  </si>
+  <si>
+    <t>2.91Y</t>
+  </si>
+  <si>
+    <t>2.0650</t>
+  </si>
+  <si>
+    <t>2.0457</t>
+  </si>
+  <si>
+    <t>0.43</t>
+  </si>
+  <si>
+    <t>08:02:16</t>
+  </si>
+  <si>
+    <t>99.4939</t>
+  </si>
+  <si>
+    <t>-0.86</t>
+  </si>
+  <si>
+    <t>2026-06-15</t>
+  </si>
+  <si>
+    <t>26恒丰银行永续债01</t>
+  </si>
+  <si>
+    <t>242680006.IB</t>
+  </si>
+  <si>
+    <t>4.81Y+N</t>
+  </si>
+  <si>
+    <t>2.0577/2.4922</t>
+  </si>
+  <si>
+    <t>-0.77</t>
+  </si>
+  <si>
+    <t>02:33:21</t>
+  </si>
+  <si>
+    <t>100.6438</t>
+  </si>
+  <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
+    <t>23华发集团MTN005</t>
+  </si>
+  <si>
+    <t>102382601.IB</t>
+  </si>
+  <si>
+    <t>66D</t>
+  </si>
+  <si>
+    <t>2.0400</t>
+  </si>
+  <si>
+    <t>2.0536</t>
+  </si>
+  <si>
+    <t>-1.36</t>
+  </si>
+  <si>
+    <t>08:14:42</t>
+  </si>
+  <si>
+    <t>B-</t>
+  </si>
+  <si>
+    <t>100.3288</t>
+  </si>
+  <si>
+    <t>江苏银行股份有限公司</t>
+  </si>
+  <si>
+    <t>2023-09-21</t>
+  </si>
+  <si>
+    <t>26凉山发展PPN001</t>
+  </si>
+  <si>
+    <t>032601530.IB</t>
+  </si>
+  <si>
+    <t>2.68Y+2.00Y</t>
+  </si>
+  <si>
+    <t>2.0000</t>
+  </si>
+  <si>
+    <t>2.0139/2.3347</t>
+  </si>
+  <si>
+    <t>-1.39</t>
+  </si>
+  <si>
+    <t>08:10:21</t>
+  </si>
+  <si>
+    <t>100.8300</t>
+  </si>
+  <si>
+    <t>中泰证券股份有限公司</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>最优买量</t>
+  </si>
+  <si>
+    <t>最优Bid</t>
+  </si>
+  <si>
+    <t>最优Ofr</t>
+  </si>
+  <si>
+    <t>最优卖量</t>
+  </si>
+  <si>
+    <t>涨跌</t>
+  </si>
+  <si>
+    <t>中债偏离(BP)</t>
+  </si>
+  <si>
+    <t>中债净价</t>
+  </si>
+  <si>
+    <t>中证偏离(BP)</t>
+  </si>
+  <si>
+    <t>Bid-中债(BP)</t>
+  </si>
+  <si>
+    <t>中债-Ofr(BP)</t>
+  </si>
+  <si>
+    <t>Ofr-中债(BP)</t>
+  </si>
+  <si>
+    <t>票面利率(%)</t>
+  </si>
+  <si>
+    <t>债券余额(亿)</t>
+  </si>
+  <si>
+    <t>到期日</t>
+  </si>
+  <si>
+    <t>YY评分</t>
+  </si>
+  <si>
+    <t>久期</t>
+  </si>
+  <si>
+    <t>发行人简称</t>
+  </si>
+  <si>
+    <t>担保人</t>
+  </si>
+  <si>
+    <t>公私募</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>成交日期</t>
   </si>
   <si>
-    <t>债券简称</t>
-  </si>
-  <si>
-    <t>剩余期限</t>
-  </si>
-  <si>
-    <t>最新成交</t>
-  </si>
-  <si>
-    <t>中债(行/到)</t>
-  </si>
-  <si>
-    <t>中债偏离(BP)</t>
-  </si>
-  <si>
-    <t>发行人简称</t>
-  </si>
-  <si>
     <t>区域</t>
   </si>
   <si>
-    <t>债券代码</t>
-  </si>
-  <si>
-    <t>中债隐含评级</t>
-  </si>
-  <si>
-    <t>中债净价</t>
-  </si>
-  <si>
-    <t>主/债</t>
-  </si>
-  <si>
-    <t>票面利率(%)</t>
-  </si>
-  <si>
-    <t>债券余额(亿)</t>
-  </si>
-  <si>
-    <t>到期日</t>
-  </si>
-  <si>
-    <t>YY评分</t>
-  </si>
-  <si>
-    <t>久期</t>
+    <t>2026-7-21</t>
+  </si>
+  <si>
+    <t>云南</t>
+  </si>
+  <si>
+    <t>湖北省联合发展投资集团有限公司</t>
+  </si>
+  <si>
+    <t>湖北</t>
+  </si>
+  <si>
+    <t>重庆</t>
+  </si>
+  <si>
+    <t>武汉开发投资有限公司</t>
+  </si>
+  <si>
+    <t>山东</t>
   </si>
 </sst>
 </file>
@@ -444,15 +1179,1382 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="12" width="10" customWidth="1"/>
+    <col min="13" max="13" width="15" customWidth="1"/>
+    <col min="14" max="15" width="10" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
+    <col min="17" max="17" width="14" customWidth="1"/>
+    <col min="18" max="18" width="10" customWidth="1"/>
+    <col min="19" max="19" width="26" customWidth="1"/>
+    <col min="20" max="20" width="10" customWidth="1"/>
+    <col min="21" max="21" width="12" customWidth="1"/>
+    <col min="22" max="22" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" t="s">
+        <v>30</v>
+      </c>
+      <c r="O2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>33</v>
+      </c>
+      <c r="R2" t="s">
+        <v>34</v>
+      </c>
+      <c r="S2" t="s">
+        <v>35</v>
+      </c>
+      <c r="T2" t="s">
+        <v>30</v>
+      </c>
+      <c r="U2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3" t="s">
+        <v>42</v>
+      </c>
+      <c r="N3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O3" t="s">
+        <v>44</v>
+      </c>
+      <c r="P3" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>33</v>
+      </c>
+      <c r="R3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S3" t="s">
+        <v>46</v>
+      </c>
+      <c r="T3" t="s">
+        <v>43</v>
+      </c>
+      <c r="U3" t="s">
+        <v>47</v>
+      </c>
+      <c r="V3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I4" t="s">
+        <v>53</v>
+      </c>
+      <c r="J4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4" t="s">
+        <v>55</v>
+      </c>
+      <c r="N4" t="s">
+        <v>56</v>
+      </c>
+      <c r="O4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P4" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>33</v>
+      </c>
+      <c r="R4" t="s">
+        <v>58</v>
+      </c>
+      <c r="S4" t="s">
+        <v>59</v>
+      </c>
+      <c r="T4" t="s">
+        <v>56</v>
+      </c>
+      <c r="U4" t="s">
+        <v>60</v>
+      </c>
+      <c r="V4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F5" t="s">
+        <v>64</v>
+      </c>
+      <c r="G5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I5" t="s">
+        <v>64</v>
+      </c>
+      <c r="J5" t="s">
+        <v>66</v>
+      </c>
+      <c r="K5" t="s">
+        <v>67</v>
+      </c>
+      <c r="L5" t="s">
+        <v>67</v>
+      </c>
+      <c r="M5" t="s">
+        <v>68</v>
+      </c>
+      <c r="N5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O5" t="s">
+        <v>70</v>
+      </c>
+      <c r="P5" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>33</v>
+      </c>
+      <c r="R5" t="s">
+        <v>72</v>
+      </c>
+      <c r="S5" t="s">
+        <v>59</v>
+      </c>
+      <c r="T5" t="s">
+        <v>69</v>
+      </c>
+      <c r="U5" t="s">
+        <v>73</v>
+      </c>
+      <c r="V5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" t="s">
+        <v>53</v>
+      </c>
+      <c r="G6" t="s">
+        <v>77</v>
+      </c>
+      <c r="H6" t="s">
+        <v>78</v>
+      </c>
+      <c r="I6" t="s">
+        <v>78</v>
+      </c>
+      <c r="J6" t="s">
+        <v>79</v>
+      </c>
+      <c r="K6" t="s">
+        <v>28</v>
+      </c>
+      <c r="L6" t="s">
+        <v>67</v>
+      </c>
+      <c r="M6" t="s">
+        <v>80</v>
+      </c>
+      <c r="N6" t="s">
+        <v>81</v>
+      </c>
+      <c r="O6" t="s">
+        <v>82</v>
+      </c>
+      <c r="P6" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>33</v>
+      </c>
+      <c r="R6" t="s">
+        <v>83</v>
+      </c>
+      <c r="S6" t="s">
+        <v>59</v>
+      </c>
+      <c r="T6" t="s">
+        <v>81</v>
+      </c>
+      <c r="U6" t="s">
+        <v>84</v>
+      </c>
+      <c r="V6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" t="s">
+        <v>87</v>
+      </c>
+      <c r="D7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E7" t="s">
+        <v>77</v>
+      </c>
+      <c r="F7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H7" t="s">
+        <v>89</v>
+      </c>
+      <c r="I7" t="s">
+        <v>88</v>
+      </c>
+      <c r="J7" t="s">
+        <v>90</v>
+      </c>
+      <c r="K7" t="s">
+        <v>79</v>
+      </c>
+      <c r="L7" t="s">
+        <v>91</v>
+      </c>
+      <c r="M7" t="s">
+        <v>92</v>
+      </c>
+      <c r="N7" t="s">
+        <v>93</v>
+      </c>
+      <c r="O7" t="s">
+        <v>94</v>
+      </c>
+      <c r="P7" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>33</v>
+      </c>
+      <c r="R7" t="s">
+        <v>95</v>
+      </c>
+      <c r="S7" t="s">
+        <v>59</v>
+      </c>
+      <c r="T7" t="s">
+        <v>93</v>
+      </c>
+      <c r="U7" t="s">
+        <v>96</v>
+      </c>
+      <c r="V7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" t="s">
+        <v>99</v>
+      </c>
+      <c r="D8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E8" t="s">
+        <v>100</v>
+      </c>
+      <c r="F8" t="s">
+        <v>100</v>
+      </c>
+      <c r="G8" t="s">
+        <v>100</v>
+      </c>
+      <c r="H8" t="s">
+        <v>100</v>
+      </c>
+      <c r="I8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" t="s">
+        <v>26</v>
+      </c>
+      <c r="K8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L8" t="s">
+        <v>28</v>
+      </c>
+      <c r="M8" t="s">
+        <v>101</v>
+      </c>
+      <c r="N8" t="s">
+        <v>102</v>
+      </c>
+      <c r="O8" t="s">
+        <v>103</v>
+      </c>
+      <c r="P8" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>33</v>
+      </c>
+      <c r="R8" t="s">
+        <v>105</v>
+      </c>
+      <c r="S8" t="s">
+        <v>106</v>
+      </c>
+      <c r="T8" t="s">
+        <v>102</v>
+      </c>
+      <c r="U8" t="s">
+        <v>107</v>
+      </c>
+      <c r="V8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B9" t="s">
+        <v>110</v>
+      </c>
+      <c r="C9" t="s">
+        <v>111</v>
+      </c>
+      <c r="D9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E9" t="s">
+        <v>112</v>
+      </c>
+      <c r="F9" t="s">
+        <v>112</v>
+      </c>
+      <c r="G9" t="s">
+        <v>112</v>
+      </c>
+      <c r="H9" t="s">
+        <v>112</v>
+      </c>
+      <c r="I9" t="s">
+        <v>100</v>
+      </c>
+      <c r="J9" t="s">
+        <v>67</v>
+      </c>
+      <c r="K9" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" t="s">
+        <v>67</v>
+      </c>
+      <c r="M9" t="s">
+        <v>113</v>
+      </c>
+      <c r="N9" t="s">
+        <v>114</v>
+      </c>
+      <c r="O9" t="s">
+        <v>115</v>
+      </c>
+      <c r="P9" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>33</v>
+      </c>
+      <c r="R9" t="s">
+        <v>117</v>
+      </c>
+      <c r="S9" t="s">
+        <v>59</v>
+      </c>
+      <c r="T9" t="s">
+        <v>114</v>
+      </c>
+      <c r="U9" t="s">
+        <v>118</v>
+      </c>
+      <c r="V9" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B10" t="s">
+        <v>121</v>
+      </c>
+      <c r="C10" t="s">
+        <v>122</v>
+      </c>
+      <c r="D10" t="s">
+        <v>123</v>
+      </c>
+      <c r="E10" t="s">
+        <v>123</v>
+      </c>
+      <c r="F10" t="s">
+        <v>123</v>
+      </c>
+      <c r="G10" t="s">
+        <v>123</v>
+      </c>
+      <c r="H10" t="s">
+        <v>123</v>
+      </c>
+      <c r="I10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K10" t="s">
+        <v>27</v>
+      </c>
+      <c r="L10" t="s">
+        <v>28</v>
+      </c>
+      <c r="M10" t="s">
+        <v>124</v>
+      </c>
+      <c r="N10" t="s">
+        <v>125</v>
+      </c>
+      <c r="O10" t="s">
+        <v>126</v>
+      </c>
+      <c r="P10" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>33</v>
+      </c>
+      <c r="R10" t="s">
+        <v>128</v>
+      </c>
+      <c r="S10" t="s">
+        <v>129</v>
+      </c>
+      <c r="T10" t="s">
+        <v>125</v>
+      </c>
+      <c r="U10" t="s">
+        <v>130</v>
+      </c>
+      <c r="V10" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>131</v>
+      </c>
+      <c r="B11" t="s">
+        <v>132</v>
+      </c>
+      <c r="C11" t="s">
+        <v>122</v>
+      </c>
+      <c r="D11" t="s">
+        <v>123</v>
+      </c>
+      <c r="E11" t="s">
+        <v>123</v>
+      </c>
+      <c r="F11" t="s">
+        <v>123</v>
+      </c>
+      <c r="G11" t="s">
+        <v>123</v>
+      </c>
+      <c r="H11" t="s">
+        <v>123</v>
+      </c>
+      <c r="I11" t="s">
+        <v>26</v>
+      </c>
+      <c r="J11" t="s">
+        <v>26</v>
+      </c>
+      <c r="K11" t="s">
+        <v>27</v>
+      </c>
+      <c r="L11" t="s">
+        <v>67</v>
+      </c>
+      <c r="M11" t="s">
+        <v>133</v>
+      </c>
+      <c r="N11" t="s">
+        <v>134</v>
+      </c>
+      <c r="O11" t="s">
+        <v>135</v>
+      </c>
+      <c r="P11" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>33</v>
+      </c>
+      <c r="R11" t="s">
+        <v>136</v>
+      </c>
+      <c r="S11" t="s">
+        <v>129</v>
+      </c>
+      <c r="T11" t="s">
+        <v>134</v>
+      </c>
+      <c r="U11" t="s">
+        <v>137</v>
+      </c>
+      <c r="V11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>138</v>
+      </c>
+      <c r="B12" t="s">
+        <v>139</v>
+      </c>
+      <c r="C12" t="s">
+        <v>140</v>
+      </c>
+      <c r="D12" t="s">
+        <v>123</v>
+      </c>
+      <c r="E12" t="s">
+        <v>123</v>
+      </c>
+      <c r="F12" t="s">
+        <v>123</v>
+      </c>
+      <c r="G12" t="s">
+        <v>123</v>
+      </c>
+      <c r="H12" t="s">
+        <v>123</v>
+      </c>
+      <c r="I12" t="s">
+        <v>141</v>
+      </c>
+      <c r="J12" t="s">
+        <v>142</v>
+      </c>
+      <c r="K12" t="s">
+        <v>27</v>
+      </c>
+      <c r="L12" t="s">
+        <v>67</v>
+      </c>
+      <c r="M12" t="s">
+        <v>143</v>
+      </c>
+      <c r="N12" t="s">
+        <v>144</v>
+      </c>
+      <c r="O12" t="s">
+        <v>145</v>
+      </c>
+      <c r="P12" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>33</v>
+      </c>
+      <c r="R12" t="s">
+        <v>147</v>
+      </c>
+      <c r="S12" t="s">
+        <v>148</v>
+      </c>
+      <c r="T12" t="s">
+        <v>144</v>
+      </c>
+      <c r="U12" t="s">
+        <v>149</v>
+      </c>
+      <c r="V12" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>150</v>
+      </c>
+      <c r="B13" t="s">
+        <v>151</v>
+      </c>
+      <c r="C13" t="s">
+        <v>152</v>
+      </c>
+      <c r="D13" t="s">
+        <v>153</v>
+      </c>
+      <c r="E13" t="s">
+        <v>153</v>
+      </c>
+      <c r="F13" t="s">
+        <v>153</v>
+      </c>
+      <c r="G13" t="s">
+        <v>153</v>
+      </c>
+      <c r="H13" t="s">
+        <v>153</v>
+      </c>
+      <c r="I13" t="s">
+        <v>26</v>
+      </c>
+      <c r="J13" t="s">
+        <v>26</v>
+      </c>
+      <c r="K13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L13" t="s">
+        <v>27</v>
+      </c>
+      <c r="M13" t="s">
+        <v>154</v>
+      </c>
+      <c r="N13" t="s">
+        <v>155</v>
+      </c>
+      <c r="O13" t="s">
+        <v>156</v>
+      </c>
+      <c r="P13" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>33</v>
+      </c>
+      <c r="R13" t="s">
+        <v>157</v>
+      </c>
+      <c r="S13" t="s">
+        <v>158</v>
+      </c>
+      <c r="T13" t="s">
+        <v>155</v>
+      </c>
+      <c r="U13" t="s">
+        <v>159</v>
+      </c>
+      <c r="V13" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>161</v>
+      </c>
+      <c r="B14" t="s">
+        <v>162</v>
+      </c>
+      <c r="C14" t="s">
+        <v>163</v>
+      </c>
+      <c r="D14" t="s">
+        <v>164</v>
+      </c>
+      <c r="E14" t="s">
+        <v>164</v>
+      </c>
+      <c r="F14" t="s">
+        <v>164</v>
+      </c>
+      <c r="G14" t="s">
+        <v>164</v>
+      </c>
+      <c r="H14" t="s">
+        <v>164</v>
+      </c>
+      <c r="I14" t="s">
+        <v>165</v>
+      </c>
+      <c r="J14" t="s">
+        <v>67</v>
+      </c>
+      <c r="K14" t="s">
+        <v>28</v>
+      </c>
+      <c r="L14" t="s">
+        <v>28</v>
+      </c>
+      <c r="M14" t="s">
+        <v>166</v>
+      </c>
+      <c r="N14" t="s">
+        <v>167</v>
+      </c>
+      <c r="O14" t="s">
+        <v>168</v>
+      </c>
+      <c r="P14" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>33</v>
+      </c>
+      <c r="R14" t="s">
+        <v>169</v>
+      </c>
+      <c r="S14" t="s">
+        <v>170</v>
+      </c>
+      <c r="T14" t="s">
+        <v>167</v>
+      </c>
+      <c r="U14" t="s">
+        <v>171</v>
+      </c>
+      <c r="V14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>172</v>
+      </c>
+      <c r="B15" t="s">
+        <v>173</v>
+      </c>
+      <c r="C15" t="s">
+        <v>174</v>
+      </c>
+      <c r="D15" t="s">
+        <v>175</v>
+      </c>
+      <c r="E15" t="s">
+        <v>175</v>
+      </c>
+      <c r="F15" t="s">
+        <v>175</v>
+      </c>
+      <c r="G15" t="s">
+        <v>175</v>
+      </c>
+      <c r="H15" t="s">
+        <v>175</v>
+      </c>
+      <c r="I15" t="s">
+        <v>26</v>
+      </c>
+      <c r="J15" t="s">
+        <v>26</v>
+      </c>
+      <c r="K15" t="s">
+        <v>67</v>
+      </c>
+      <c r="L15" t="s">
+        <v>28</v>
+      </c>
+      <c r="M15" t="s">
+        <v>176</v>
+      </c>
+      <c r="N15" t="s">
+        <v>56</v>
+      </c>
+      <c r="O15" t="s">
+        <v>177</v>
+      </c>
+      <c r="P15" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>33</v>
+      </c>
+      <c r="R15" t="s">
+        <v>178</v>
+      </c>
+      <c r="S15" t="s">
+        <v>179</v>
+      </c>
+      <c r="T15" t="s">
+        <v>180</v>
+      </c>
+      <c r="U15" t="s">
+        <v>181</v>
+      </c>
+      <c r="V15" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>183</v>
+      </c>
+      <c r="B16" t="s">
+        <v>184</v>
+      </c>
+      <c r="C16" t="s">
+        <v>185</v>
+      </c>
+      <c r="D16" t="s">
+        <v>186</v>
+      </c>
+      <c r="E16" t="s">
+        <v>187</v>
+      </c>
+      <c r="F16" t="s">
+        <v>187</v>
+      </c>
+      <c r="G16" t="s">
+        <v>186</v>
+      </c>
+      <c r="H16" t="s">
+        <v>188</v>
+      </c>
+      <c r="I16" t="s">
+        <v>189</v>
+      </c>
+      <c r="J16" t="s">
+        <v>30</v>
+      </c>
+      <c r="K16" t="s">
+        <v>28</v>
+      </c>
+      <c r="L16" t="s">
+        <v>79</v>
+      </c>
+      <c r="M16" t="s">
+        <v>190</v>
+      </c>
+      <c r="N16" t="s">
+        <v>191</v>
+      </c>
+      <c r="O16" t="s">
+        <v>192</v>
+      </c>
+      <c r="P16" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>33</v>
+      </c>
+      <c r="R16" t="s">
+        <v>193</v>
+      </c>
+      <c r="S16" t="s">
+        <v>59</v>
+      </c>
+      <c r="T16" t="s">
+        <v>191</v>
+      </c>
+      <c r="U16" t="s">
+        <v>194</v>
+      </c>
+      <c r="V16" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>195</v>
+      </c>
+      <c r="B17" t="s">
+        <v>196</v>
+      </c>
+      <c r="C17" t="s">
+        <v>197</v>
+      </c>
+      <c r="D17" t="s">
+        <v>189</v>
+      </c>
+      <c r="E17" t="s">
+        <v>189</v>
+      </c>
+      <c r="F17" t="s">
+        <v>189</v>
+      </c>
+      <c r="G17" t="s">
+        <v>189</v>
+      </c>
+      <c r="H17" t="s">
+        <v>189</v>
+      </c>
+      <c r="I17" t="s">
+        <v>198</v>
+      </c>
+      <c r="J17" t="s">
+        <v>28</v>
+      </c>
+      <c r="K17" t="s">
+        <v>28</v>
+      </c>
+      <c r="L17" t="s">
+        <v>27</v>
+      </c>
+      <c r="M17" t="s">
+        <v>199</v>
+      </c>
+      <c r="N17" t="s">
+        <v>200</v>
+      </c>
+      <c r="O17" t="s">
+        <v>201</v>
+      </c>
+      <c r="P17" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>33</v>
+      </c>
+      <c r="R17" t="s">
+        <v>202</v>
+      </c>
+      <c r="S17" t="s">
+        <v>148</v>
+      </c>
+      <c r="T17" t="s">
+        <v>203</v>
+      </c>
+      <c r="U17" t="s">
+        <v>204</v>
+      </c>
+      <c r="V17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>205</v>
+      </c>
+      <c r="B18" t="s">
+        <v>206</v>
+      </c>
+      <c r="C18" t="s">
+        <v>207</v>
+      </c>
+      <c r="D18" t="s">
+        <v>189</v>
+      </c>
+      <c r="E18" t="s">
+        <v>189</v>
+      </c>
+      <c r="F18" t="s">
+        <v>189</v>
+      </c>
+      <c r="G18" t="s">
+        <v>189</v>
+      </c>
+      <c r="H18" t="s">
+        <v>189</v>
+      </c>
+      <c r="I18" t="s">
+        <v>189</v>
+      </c>
+      <c r="J18" t="s">
+        <v>90</v>
+      </c>
+      <c r="K18" t="s">
+        <v>27</v>
+      </c>
+      <c r="L18" t="s">
+        <v>67</v>
+      </c>
+      <c r="M18" t="s">
+        <v>208</v>
+      </c>
+      <c r="N18" t="s">
+        <v>209</v>
+      </c>
+      <c r="O18" t="s">
+        <v>210</v>
+      </c>
+      <c r="P18" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>33</v>
+      </c>
+      <c r="R18" t="s">
+        <v>211</v>
+      </c>
+      <c r="S18" t="s">
+        <v>59</v>
+      </c>
+      <c r="T18" t="s">
+        <v>209</v>
+      </c>
+      <c r="U18" t="s">
+        <v>212</v>
+      </c>
+      <c r="V18" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>213</v>
+      </c>
+      <c r="B19" t="s">
+        <v>214</v>
+      </c>
+      <c r="C19" t="s">
+        <v>215</v>
+      </c>
+      <c r="D19" t="s">
+        <v>216</v>
+      </c>
+      <c r="E19" t="s">
+        <v>216</v>
+      </c>
+      <c r="F19" t="s">
+        <v>216</v>
+      </c>
+      <c r="G19" t="s">
+        <v>216</v>
+      </c>
+      <c r="H19" t="s">
+        <v>216</v>
+      </c>
+      <c r="I19" t="s">
+        <v>26</v>
+      </c>
+      <c r="J19" t="s">
+        <v>26</v>
+      </c>
+      <c r="K19" t="s">
+        <v>28</v>
+      </c>
+      <c r="L19" t="s">
+        <v>27</v>
+      </c>
+      <c r="M19" t="s">
+        <v>217</v>
+      </c>
+      <c r="N19" t="s">
+        <v>218</v>
+      </c>
+      <c r="O19" t="s">
+        <v>219</v>
+      </c>
+      <c r="P19" t="s">
+        <v>220</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>33</v>
+      </c>
+      <c r="R19" t="s">
+        <v>221</v>
+      </c>
+      <c r="S19" t="s">
+        <v>222</v>
+      </c>
+      <c r="T19" t="s">
+        <v>218</v>
+      </c>
+      <c r="U19" t="s">
+        <v>223</v>
+      </c>
+      <c r="V19" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>224</v>
+      </c>
+      <c r="B20" t="s">
+        <v>225</v>
+      </c>
+      <c r="C20" t="s">
+        <v>226</v>
+      </c>
+      <c r="D20" t="s">
+        <v>227</v>
+      </c>
+      <c r="E20" t="s">
+        <v>227</v>
+      </c>
+      <c r="F20" t="s">
+        <v>227</v>
+      </c>
+      <c r="G20" t="s">
+        <v>227</v>
+      </c>
+      <c r="H20" t="s">
+        <v>227</v>
+      </c>
+      <c r="I20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J20" t="s">
+        <v>26</v>
+      </c>
+      <c r="K20" t="s">
+        <v>27</v>
+      </c>
+      <c r="L20" t="s">
+        <v>28</v>
+      </c>
+      <c r="M20" t="s">
+        <v>228</v>
+      </c>
+      <c r="N20" t="s">
+        <v>229</v>
+      </c>
+      <c r="O20" t="s">
+        <v>230</v>
+      </c>
+      <c r="P20" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>33</v>
+      </c>
+      <c r="R20" t="s">
+        <v>231</v>
+      </c>
+      <c r="S20" t="s">
+        <v>232</v>
+      </c>
+      <c r="T20" t="s">
+        <v>229</v>
+      </c>
+      <c r="U20" t="s">
+        <v>233</v>
+      </c>
+      <c r="V20" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -463,15 +2565,1745 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:AB20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="11" width="10" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="13" max="13" width="14" customWidth="1"/>
+    <col min="14" max="14" width="15" customWidth="1"/>
+    <col min="15" max="15" width="10" customWidth="1"/>
+    <col min="16" max="16" width="14" customWidth="1"/>
+    <col min="17" max="17" width="10" customWidth="1"/>
+    <col min="18" max="20" width="14" customWidth="1"/>
+    <col min="21" max="21" width="13" customWidth="1"/>
+    <col min="22" max="22" width="14" customWidth="1"/>
+    <col min="23" max="25" width="10" customWidth="1"/>
+    <col min="26" max="26" width="12" customWidth="1"/>
+    <col min="27" max="28" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>234</v>
+      </c>
+      <c r="E1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F1" t="s">
+        <v>236</v>
+      </c>
+      <c r="G1" t="s">
+        <v>237</v>
+      </c>
+      <c r="H1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>238</v>
+      </c>
+      <c r="K1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" t="s">
+        <v>239</v>
+      </c>
+      <c r="N1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P1" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>21</v>
+      </c>
+      <c r="R1" t="s">
+        <v>242</v>
+      </c>
+      <c r="S1" t="s">
+        <v>243</v>
+      </c>
+      <c r="T1" t="s">
+        <v>244</v>
+      </c>
+      <c r="U1" t="s">
+        <v>245</v>
+      </c>
+      <c r="V1" t="s">
+        <v>246</v>
+      </c>
+      <c r="W1" t="s">
+        <v>247</v>
+      </c>
+      <c r="X1" t="s">
+        <v>248</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>249</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>250</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>251</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E2" t="s">
+        <v>253</v>
+      </c>
+      <c r="F2" t="s">
+        <v>253</v>
+      </c>
+      <c r="G2" t="s">
+        <v>253</v>
+      </c>
+      <c r="H2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" t="s">
+        <v>253</v>
+      </c>
+      <c r="K2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M2" t="s">
+        <v>253</v>
+      </c>
+      <c r="N2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O2" t="s">
+        <v>253</v>
+      </c>
+      <c r="P2" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R2" t="s">
+        <v>253</v>
+      </c>
+      <c r="S2" t="s">
+        <v>253</v>
+      </c>
+      <c r="T2" t="s">
+        <v>253</v>
+      </c>
+      <c r="U2" t="s">
+        <v>253</v>
+      </c>
+      <c r="V2" t="s">
+        <v>253</v>
+      </c>
+      <c r="W2" t="s">
+        <v>253</v>
+      </c>
+      <c r="X2" t="s">
+        <v>253</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>253</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>253</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F3" t="s">
+        <v>253</v>
+      </c>
+      <c r="G3" t="s">
+        <v>253</v>
+      </c>
+      <c r="H3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" t="s">
+        <v>253</v>
+      </c>
+      <c r="K3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3" t="s">
+        <v>253</v>
+      </c>
+      <c r="N3" t="s">
+        <v>42</v>
+      </c>
+      <c r="O3" t="s">
+        <v>253</v>
+      </c>
+      <c r="P3" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>48</v>
+      </c>
+      <c r="R3" t="s">
+        <v>253</v>
+      </c>
+      <c r="S3" t="s">
+        <v>253</v>
+      </c>
+      <c r="T3" t="s">
+        <v>253</v>
+      </c>
+      <c r="U3" t="s">
+        <v>253</v>
+      </c>
+      <c r="V3" t="s">
+        <v>253</v>
+      </c>
+      <c r="W3" t="s">
+        <v>253</v>
+      </c>
+      <c r="X3" t="s">
+        <v>253</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>253</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>253</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" t="s">
+        <v>253</v>
+      </c>
+      <c r="E4" t="s">
+        <v>253</v>
+      </c>
+      <c r="F4" t="s">
+        <v>253</v>
+      </c>
+      <c r="G4" t="s">
+        <v>253</v>
+      </c>
+      <c r="H4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I4" t="s">
+        <v>53</v>
+      </c>
+      <c r="J4" t="s">
+        <v>253</v>
+      </c>
+      <c r="K4" t="s">
+        <v>57</v>
+      </c>
+      <c r="L4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" t="s">
+        <v>253</v>
+      </c>
+      <c r="N4" t="s">
+        <v>55</v>
+      </c>
+      <c r="O4" t="s">
+        <v>253</v>
+      </c>
+      <c r="P4" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>48</v>
+      </c>
+      <c r="R4" t="s">
+        <v>253</v>
+      </c>
+      <c r="S4" t="s">
+        <v>253</v>
+      </c>
+      <c r="T4" t="s">
+        <v>253</v>
+      </c>
+      <c r="U4" t="s">
+        <v>253</v>
+      </c>
+      <c r="V4" t="s">
+        <v>253</v>
+      </c>
+      <c r="W4" t="s">
+        <v>253</v>
+      </c>
+      <c r="X4" t="s">
+        <v>253</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>253</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>253</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" t="s">
+        <v>253</v>
+      </c>
+      <c r="E5" t="s">
+        <v>253</v>
+      </c>
+      <c r="F5" t="s">
+        <v>253</v>
+      </c>
+      <c r="G5" t="s">
+        <v>253</v>
+      </c>
+      <c r="H5" t="s">
+        <v>53</v>
+      </c>
+      <c r="I5" t="s">
+        <v>64</v>
+      </c>
+      <c r="J5" t="s">
+        <v>253</v>
+      </c>
+      <c r="K5" t="s">
+        <v>70</v>
+      </c>
+      <c r="L5" t="s">
+        <v>71</v>
+      </c>
+      <c r="M5" t="s">
+        <v>253</v>
+      </c>
+      <c r="N5" t="s">
+        <v>68</v>
+      </c>
+      <c r="O5" t="s">
+        <v>253</v>
+      </c>
+      <c r="P5" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>48</v>
+      </c>
+      <c r="R5" t="s">
+        <v>253</v>
+      </c>
+      <c r="S5" t="s">
+        <v>253</v>
+      </c>
+      <c r="T5" t="s">
+        <v>253</v>
+      </c>
+      <c r="U5" t="s">
+        <v>253</v>
+      </c>
+      <c r="V5" t="s">
+        <v>253</v>
+      </c>
+      <c r="W5" t="s">
+        <v>253</v>
+      </c>
+      <c r="X5" t="s">
+        <v>253</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>253</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>253</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D6" t="s">
+        <v>253</v>
+      </c>
+      <c r="E6" t="s">
+        <v>253</v>
+      </c>
+      <c r="F6" t="s">
+        <v>253</v>
+      </c>
+      <c r="G6" t="s">
+        <v>253</v>
+      </c>
+      <c r="H6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I6" t="s">
+        <v>78</v>
+      </c>
+      <c r="J6" t="s">
+        <v>253</v>
+      </c>
+      <c r="K6" t="s">
+        <v>82</v>
+      </c>
+      <c r="L6" t="s">
+        <v>71</v>
+      </c>
+      <c r="M6" t="s">
+        <v>253</v>
+      </c>
+      <c r="N6" t="s">
+        <v>80</v>
+      </c>
+      <c r="O6" t="s">
+        <v>253</v>
+      </c>
+      <c r="P6" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>48</v>
+      </c>
+      <c r="R6" t="s">
+        <v>253</v>
+      </c>
+      <c r="S6" t="s">
+        <v>253</v>
+      </c>
+      <c r="T6" t="s">
+        <v>253</v>
+      </c>
+      <c r="U6" t="s">
+        <v>253</v>
+      </c>
+      <c r="V6" t="s">
+        <v>253</v>
+      </c>
+      <c r="W6" t="s">
+        <v>253</v>
+      </c>
+      <c r="X6" t="s">
+        <v>253</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>253</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>253</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D7" t="s">
+        <v>253</v>
+      </c>
+      <c r="E7" t="s">
+        <v>253</v>
+      </c>
+      <c r="F7" t="s">
+        <v>253</v>
+      </c>
+      <c r="G7" t="s">
+        <v>253</v>
+      </c>
+      <c r="H7" t="s">
+        <v>88</v>
+      </c>
+      <c r="I7" t="s">
+        <v>88</v>
+      </c>
+      <c r="J7" t="s">
+        <v>253</v>
+      </c>
+      <c r="K7" t="s">
+        <v>94</v>
+      </c>
+      <c r="L7" t="s">
+        <v>71</v>
+      </c>
+      <c r="M7" t="s">
+        <v>253</v>
+      </c>
+      <c r="N7" t="s">
+        <v>92</v>
+      </c>
+      <c r="O7" t="s">
+        <v>253</v>
+      </c>
+      <c r="P7" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>48</v>
+      </c>
+      <c r="R7" t="s">
+        <v>253</v>
+      </c>
+      <c r="S7" t="s">
+        <v>253</v>
+      </c>
+      <c r="T7" t="s">
+        <v>253</v>
+      </c>
+      <c r="U7" t="s">
+        <v>253</v>
+      </c>
+      <c r="V7" t="s">
+        <v>253</v>
+      </c>
+      <c r="W7" t="s">
+        <v>253</v>
+      </c>
+      <c r="X7" t="s">
+        <v>253</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>253</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>99</v>
+      </c>
+      <c r="B8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D8" t="s">
+        <v>253</v>
+      </c>
+      <c r="E8" t="s">
+        <v>253</v>
+      </c>
+      <c r="F8" t="s">
+        <v>253</v>
+      </c>
+      <c r="G8" t="s">
+        <v>253</v>
+      </c>
+      <c r="H8" t="s">
+        <v>100</v>
+      </c>
+      <c r="I8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" t="s">
+        <v>253</v>
+      </c>
+      <c r="K8" t="s">
+        <v>103</v>
+      </c>
+      <c r="L8" t="s">
+        <v>104</v>
+      </c>
+      <c r="M8" t="s">
+        <v>253</v>
+      </c>
+      <c r="N8" t="s">
+        <v>101</v>
+      </c>
+      <c r="O8" t="s">
+        <v>253</v>
+      </c>
+      <c r="P8" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>108</v>
+      </c>
+      <c r="R8" t="s">
+        <v>253</v>
+      </c>
+      <c r="S8" t="s">
+        <v>253</v>
+      </c>
+      <c r="T8" t="s">
+        <v>253</v>
+      </c>
+      <c r="U8" t="s">
+        <v>253</v>
+      </c>
+      <c r="V8" t="s">
+        <v>253</v>
+      </c>
+      <c r="W8" t="s">
+        <v>253</v>
+      </c>
+      <c r="X8" t="s">
+        <v>253</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>253</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>253</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>111</v>
+      </c>
+      <c r="B9" t="s">
+        <v>109</v>
+      </c>
+      <c r="C9" t="s">
+        <v>110</v>
+      </c>
+      <c r="D9" t="s">
+        <v>253</v>
+      </c>
+      <c r="E9" t="s">
+        <v>253</v>
+      </c>
+      <c r="F9" t="s">
+        <v>253</v>
+      </c>
+      <c r="G9" t="s">
+        <v>253</v>
+      </c>
+      <c r="H9" t="s">
+        <v>112</v>
+      </c>
+      <c r="I9" t="s">
+        <v>100</v>
+      </c>
+      <c r="J9" t="s">
+        <v>253</v>
+      </c>
+      <c r="K9" t="s">
+        <v>115</v>
+      </c>
+      <c r="L9" t="s">
+        <v>116</v>
+      </c>
+      <c r="M9" t="s">
+        <v>253</v>
+      </c>
+      <c r="N9" t="s">
+        <v>113</v>
+      </c>
+      <c r="O9" t="s">
+        <v>253</v>
+      </c>
+      <c r="P9" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>119</v>
+      </c>
+      <c r="R9" t="s">
+        <v>253</v>
+      </c>
+      <c r="S9" t="s">
+        <v>253</v>
+      </c>
+      <c r="T9" t="s">
+        <v>253</v>
+      </c>
+      <c r="U9" t="s">
+        <v>253</v>
+      </c>
+      <c r="V9" t="s">
+        <v>253</v>
+      </c>
+      <c r="W9" t="s">
+        <v>253</v>
+      </c>
+      <c r="X9" t="s">
+        <v>253</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>253</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>253</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>122</v>
+      </c>
+      <c r="B10" t="s">
+        <v>120</v>
+      </c>
+      <c r="C10" t="s">
+        <v>121</v>
+      </c>
+      <c r="D10" t="s">
+        <v>253</v>
+      </c>
+      <c r="E10" t="s">
+        <v>253</v>
+      </c>
+      <c r="F10" t="s">
+        <v>253</v>
+      </c>
+      <c r="G10" t="s">
+        <v>253</v>
+      </c>
+      <c r="H10" t="s">
+        <v>123</v>
+      </c>
+      <c r="I10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10" t="s">
+        <v>253</v>
+      </c>
+      <c r="K10" t="s">
+        <v>126</v>
+      </c>
+      <c r="L10" t="s">
+        <v>127</v>
+      </c>
+      <c r="M10" t="s">
+        <v>253</v>
+      </c>
+      <c r="N10" t="s">
+        <v>124</v>
+      </c>
+      <c r="O10" t="s">
+        <v>253</v>
+      </c>
+      <c r="P10" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>108</v>
+      </c>
+      <c r="R10" t="s">
+        <v>253</v>
+      </c>
+      <c r="S10" t="s">
+        <v>253</v>
+      </c>
+      <c r="T10" t="s">
+        <v>253</v>
+      </c>
+      <c r="U10" t="s">
+        <v>253</v>
+      </c>
+      <c r="V10" t="s">
+        <v>253</v>
+      </c>
+      <c r="W10" t="s">
+        <v>253</v>
+      </c>
+      <c r="X10" t="s">
+        <v>253</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>253</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>253</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B11" t="s">
+        <v>131</v>
+      </c>
+      <c r="C11" t="s">
+        <v>132</v>
+      </c>
+      <c r="D11" t="s">
+        <v>253</v>
+      </c>
+      <c r="E11" t="s">
+        <v>253</v>
+      </c>
+      <c r="F11" t="s">
+        <v>253</v>
+      </c>
+      <c r="G11" t="s">
+        <v>253</v>
+      </c>
+      <c r="H11" t="s">
+        <v>123</v>
+      </c>
+      <c r="I11" t="s">
+        <v>26</v>
+      </c>
+      <c r="J11" t="s">
+        <v>253</v>
+      </c>
+      <c r="K11" t="s">
+        <v>135</v>
+      </c>
+      <c r="L11" t="s">
+        <v>104</v>
+      </c>
+      <c r="M11" t="s">
+        <v>253</v>
+      </c>
+      <c r="N11" t="s">
+        <v>133</v>
+      </c>
+      <c r="O11" t="s">
+        <v>253</v>
+      </c>
+      <c r="P11" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>108</v>
+      </c>
+      <c r="R11" t="s">
+        <v>253</v>
+      </c>
+      <c r="S11" t="s">
+        <v>253</v>
+      </c>
+      <c r="T11" t="s">
+        <v>253</v>
+      </c>
+      <c r="U11" t="s">
+        <v>253</v>
+      </c>
+      <c r="V11" t="s">
+        <v>253</v>
+      </c>
+      <c r="W11" t="s">
+        <v>253</v>
+      </c>
+      <c r="X11" t="s">
+        <v>253</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>253</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>253</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>140</v>
+      </c>
+      <c r="B12" t="s">
+        <v>138</v>
+      </c>
+      <c r="C12" t="s">
+        <v>139</v>
+      </c>
+      <c r="D12" t="s">
+        <v>253</v>
+      </c>
+      <c r="E12" t="s">
+        <v>253</v>
+      </c>
+      <c r="F12" t="s">
+        <v>253</v>
+      </c>
+      <c r="G12" t="s">
+        <v>253</v>
+      </c>
+      <c r="H12" t="s">
+        <v>123</v>
+      </c>
+      <c r="I12" t="s">
+        <v>141</v>
+      </c>
+      <c r="J12" t="s">
+        <v>253</v>
+      </c>
+      <c r="K12" t="s">
+        <v>145</v>
+      </c>
+      <c r="L12" t="s">
+        <v>146</v>
+      </c>
+      <c r="M12" t="s">
+        <v>253</v>
+      </c>
+      <c r="N12" t="s">
+        <v>143</v>
+      </c>
+      <c r="O12" t="s">
+        <v>253</v>
+      </c>
+      <c r="P12" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>108</v>
+      </c>
+      <c r="R12" t="s">
+        <v>253</v>
+      </c>
+      <c r="S12" t="s">
+        <v>253</v>
+      </c>
+      <c r="T12" t="s">
+        <v>253</v>
+      </c>
+      <c r="U12" t="s">
+        <v>253</v>
+      </c>
+      <c r="V12" t="s">
+        <v>253</v>
+      </c>
+      <c r="W12" t="s">
+        <v>253</v>
+      </c>
+      <c r="X12" t="s">
+        <v>253</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>253</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>253</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>152</v>
+      </c>
+      <c r="B13" t="s">
+        <v>150</v>
+      </c>
+      <c r="C13" t="s">
+        <v>151</v>
+      </c>
+      <c r="D13" t="s">
+        <v>253</v>
+      </c>
+      <c r="E13" t="s">
+        <v>253</v>
+      </c>
+      <c r="F13" t="s">
+        <v>253</v>
+      </c>
+      <c r="G13" t="s">
+        <v>253</v>
+      </c>
+      <c r="H13" t="s">
+        <v>153</v>
+      </c>
+      <c r="I13" t="s">
+        <v>26</v>
+      </c>
+      <c r="J13" t="s">
+        <v>253</v>
+      </c>
+      <c r="K13" t="s">
+        <v>156</v>
+      </c>
+      <c r="L13" t="s">
+        <v>104</v>
+      </c>
+      <c r="M13" t="s">
+        <v>253</v>
+      </c>
+      <c r="N13" t="s">
+        <v>154</v>
+      </c>
+      <c r="O13" t="s">
+        <v>253</v>
+      </c>
+      <c r="P13" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>160</v>
+      </c>
+      <c r="R13" t="s">
+        <v>253</v>
+      </c>
+      <c r="S13" t="s">
+        <v>253</v>
+      </c>
+      <c r="T13" t="s">
+        <v>253</v>
+      </c>
+      <c r="U13" t="s">
+        <v>253</v>
+      </c>
+      <c r="V13" t="s">
+        <v>253</v>
+      </c>
+      <c r="W13" t="s">
+        <v>253</v>
+      </c>
+      <c r="X13" t="s">
+        <v>253</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>253</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>253</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>163</v>
+      </c>
+      <c r="B14" t="s">
+        <v>161</v>
+      </c>
+      <c r="C14" t="s">
+        <v>162</v>
+      </c>
+      <c r="D14" t="s">
+        <v>253</v>
+      </c>
+      <c r="E14" t="s">
+        <v>253</v>
+      </c>
+      <c r="F14" t="s">
+        <v>253</v>
+      </c>
+      <c r="G14" t="s">
+        <v>253</v>
+      </c>
+      <c r="H14" t="s">
+        <v>164</v>
+      </c>
+      <c r="I14" t="s">
+        <v>165</v>
+      </c>
+      <c r="J14" t="s">
+        <v>253</v>
+      </c>
+      <c r="K14" t="s">
+        <v>168</v>
+      </c>
+      <c r="L14" t="s">
+        <v>71</v>
+      </c>
+      <c r="M14" t="s">
+        <v>253</v>
+      </c>
+      <c r="N14" t="s">
+        <v>166</v>
+      </c>
+      <c r="O14" t="s">
+        <v>253</v>
+      </c>
+      <c r="P14" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>48</v>
+      </c>
+      <c r="R14" t="s">
+        <v>253</v>
+      </c>
+      <c r="S14" t="s">
+        <v>253</v>
+      </c>
+      <c r="T14" t="s">
+        <v>253</v>
+      </c>
+      <c r="U14" t="s">
+        <v>253</v>
+      </c>
+      <c r="V14" t="s">
+        <v>253</v>
+      </c>
+      <c r="W14" t="s">
+        <v>253</v>
+      </c>
+      <c r="X14" t="s">
+        <v>253</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>253</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>253</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>174</v>
+      </c>
+      <c r="B15" t="s">
+        <v>172</v>
+      </c>
+      <c r="C15" t="s">
+        <v>173</v>
+      </c>
+      <c r="D15" t="s">
+        <v>253</v>
+      </c>
+      <c r="E15" t="s">
+        <v>253</v>
+      </c>
+      <c r="F15" t="s">
+        <v>253</v>
+      </c>
+      <c r="G15" t="s">
+        <v>253</v>
+      </c>
+      <c r="H15" t="s">
+        <v>175</v>
+      </c>
+      <c r="I15" t="s">
+        <v>26</v>
+      </c>
+      <c r="J15" t="s">
+        <v>253</v>
+      </c>
+      <c r="K15" t="s">
+        <v>177</v>
+      </c>
+      <c r="L15" t="s">
+        <v>32</v>
+      </c>
+      <c r="M15" t="s">
+        <v>253</v>
+      </c>
+      <c r="N15" t="s">
+        <v>176</v>
+      </c>
+      <c r="O15" t="s">
+        <v>253</v>
+      </c>
+      <c r="P15" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>182</v>
+      </c>
+      <c r="R15" t="s">
+        <v>253</v>
+      </c>
+      <c r="S15" t="s">
+        <v>253</v>
+      </c>
+      <c r="T15" t="s">
+        <v>253</v>
+      </c>
+      <c r="U15" t="s">
+        <v>253</v>
+      </c>
+      <c r="V15" t="s">
+        <v>253</v>
+      </c>
+      <c r="W15" t="s">
+        <v>253</v>
+      </c>
+      <c r="X15" t="s">
+        <v>253</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>253</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>253</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B16" t="s">
+        <v>183</v>
+      </c>
+      <c r="C16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D16" t="s">
+        <v>253</v>
+      </c>
+      <c r="E16" t="s">
+        <v>253</v>
+      </c>
+      <c r="F16" t="s">
+        <v>253</v>
+      </c>
+      <c r="G16" t="s">
+        <v>253</v>
+      </c>
+      <c r="H16" t="s">
+        <v>186</v>
+      </c>
+      <c r="I16" t="s">
+        <v>189</v>
+      </c>
+      <c r="J16" t="s">
+        <v>253</v>
+      </c>
+      <c r="K16" t="s">
+        <v>192</v>
+      </c>
+      <c r="L16" t="s">
+        <v>71</v>
+      </c>
+      <c r="M16" t="s">
+        <v>253</v>
+      </c>
+      <c r="N16" t="s">
+        <v>190</v>
+      </c>
+      <c r="O16" t="s">
+        <v>253</v>
+      </c>
+      <c r="P16" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>48</v>
+      </c>
+      <c r="R16" t="s">
+        <v>253</v>
+      </c>
+      <c r="S16" t="s">
+        <v>253</v>
+      </c>
+      <c r="T16" t="s">
+        <v>253</v>
+      </c>
+      <c r="U16" t="s">
+        <v>253</v>
+      </c>
+      <c r="V16" t="s">
+        <v>253</v>
+      </c>
+      <c r="W16" t="s">
+        <v>253</v>
+      </c>
+      <c r="X16" t="s">
+        <v>253</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>253</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>253</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>197</v>
+      </c>
+      <c r="B17" t="s">
+        <v>195</v>
+      </c>
+      <c r="C17" t="s">
+        <v>196</v>
+      </c>
+      <c r="D17" t="s">
+        <v>253</v>
+      </c>
+      <c r="E17" t="s">
+        <v>253</v>
+      </c>
+      <c r="F17" t="s">
+        <v>253</v>
+      </c>
+      <c r="G17" t="s">
+        <v>253</v>
+      </c>
+      <c r="H17" t="s">
+        <v>189</v>
+      </c>
+      <c r="I17" t="s">
+        <v>198</v>
+      </c>
+      <c r="J17" t="s">
+        <v>253</v>
+      </c>
+      <c r="K17" t="s">
+        <v>201</v>
+      </c>
+      <c r="L17" t="s">
+        <v>116</v>
+      </c>
+      <c r="M17" t="s">
+        <v>253</v>
+      </c>
+      <c r="N17" t="s">
+        <v>199</v>
+      </c>
+      <c r="O17" t="s">
+        <v>253</v>
+      </c>
+      <c r="P17" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>48</v>
+      </c>
+      <c r="R17" t="s">
+        <v>253</v>
+      </c>
+      <c r="S17" t="s">
+        <v>253</v>
+      </c>
+      <c r="T17" t="s">
+        <v>253</v>
+      </c>
+      <c r="U17" t="s">
+        <v>253</v>
+      </c>
+      <c r="V17" t="s">
+        <v>253</v>
+      </c>
+      <c r="W17" t="s">
+        <v>253</v>
+      </c>
+      <c r="X17" t="s">
+        <v>253</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>253</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>253</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>207</v>
+      </c>
+      <c r="B18" t="s">
+        <v>205</v>
+      </c>
+      <c r="C18" t="s">
+        <v>206</v>
+      </c>
+      <c r="D18" t="s">
+        <v>253</v>
+      </c>
+      <c r="E18" t="s">
+        <v>253</v>
+      </c>
+      <c r="F18" t="s">
+        <v>253</v>
+      </c>
+      <c r="G18" t="s">
+        <v>253</v>
+      </c>
+      <c r="H18" t="s">
+        <v>189</v>
+      </c>
+      <c r="I18" t="s">
+        <v>189</v>
+      </c>
+      <c r="J18" t="s">
+        <v>253</v>
+      </c>
+      <c r="K18" t="s">
+        <v>210</v>
+      </c>
+      <c r="L18" t="s">
+        <v>71</v>
+      </c>
+      <c r="M18" t="s">
+        <v>253</v>
+      </c>
+      <c r="N18" t="s">
+        <v>208</v>
+      </c>
+      <c r="O18" t="s">
+        <v>253</v>
+      </c>
+      <c r="P18" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>48</v>
+      </c>
+      <c r="R18" t="s">
+        <v>253</v>
+      </c>
+      <c r="S18" t="s">
+        <v>253</v>
+      </c>
+      <c r="T18" t="s">
+        <v>253</v>
+      </c>
+      <c r="U18" t="s">
+        <v>253</v>
+      </c>
+      <c r="V18" t="s">
+        <v>253</v>
+      </c>
+      <c r="W18" t="s">
+        <v>253</v>
+      </c>
+      <c r="X18" t="s">
+        <v>253</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>253</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>253</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>215</v>
+      </c>
+      <c r="B19" t="s">
+        <v>213</v>
+      </c>
+      <c r="C19" t="s">
+        <v>214</v>
+      </c>
+      <c r="D19" t="s">
+        <v>253</v>
+      </c>
+      <c r="E19" t="s">
+        <v>253</v>
+      </c>
+      <c r="F19" t="s">
+        <v>253</v>
+      </c>
+      <c r="G19" t="s">
+        <v>253</v>
+      </c>
+      <c r="H19" t="s">
+        <v>216</v>
+      </c>
+      <c r="I19" t="s">
+        <v>26</v>
+      </c>
+      <c r="J19" t="s">
+        <v>253</v>
+      </c>
+      <c r="K19" t="s">
+        <v>219</v>
+      </c>
+      <c r="L19" t="s">
+        <v>220</v>
+      </c>
+      <c r="M19" t="s">
+        <v>253</v>
+      </c>
+      <c r="N19" t="s">
+        <v>217</v>
+      </c>
+      <c r="O19" t="s">
+        <v>253</v>
+      </c>
+      <c r="P19" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>48</v>
+      </c>
+      <c r="R19" t="s">
+        <v>253</v>
+      </c>
+      <c r="S19" t="s">
+        <v>253</v>
+      </c>
+      <c r="T19" t="s">
+        <v>253</v>
+      </c>
+      <c r="U19" t="s">
+        <v>253</v>
+      </c>
+      <c r="V19" t="s">
+        <v>253</v>
+      </c>
+      <c r="W19" t="s">
+        <v>253</v>
+      </c>
+      <c r="X19" t="s">
+        <v>253</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>253</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>253</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>226</v>
+      </c>
+      <c r="B20" t="s">
+        <v>224</v>
+      </c>
+      <c r="C20" t="s">
+        <v>225</v>
+      </c>
+      <c r="D20" t="s">
+        <v>253</v>
+      </c>
+      <c r="E20" t="s">
+        <v>253</v>
+      </c>
+      <c r="F20" t="s">
+        <v>253</v>
+      </c>
+      <c r="G20" t="s">
+        <v>253</v>
+      </c>
+      <c r="H20" t="s">
+        <v>227</v>
+      </c>
+      <c r="I20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J20" t="s">
+        <v>253</v>
+      </c>
+      <c r="K20" t="s">
+        <v>230</v>
+      </c>
+      <c r="L20" t="s">
+        <v>127</v>
+      </c>
+      <c r="M20" t="s">
+        <v>253</v>
+      </c>
+      <c r="N20" t="s">
+        <v>228</v>
+      </c>
+      <c r="O20" t="s">
+        <v>253</v>
+      </c>
+      <c r="P20" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>108</v>
+      </c>
+      <c r="R20" t="s">
+        <v>253</v>
+      </c>
+      <c r="S20" t="s">
+        <v>253</v>
+      </c>
+      <c r="T20" t="s">
+        <v>253</v>
+      </c>
+      <c r="U20" t="s">
+        <v>253</v>
+      </c>
+      <c r="V20" t="s">
+        <v>253</v>
+      </c>
+      <c r="W20" t="s">
+        <v>253</v>
+      </c>
+      <c r="X20" t="s">
+        <v>253</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>253</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>253</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>253</v>
       </c>
     </row>
   </sheetData>
@@ -482,15 +4314,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="7" max="7" width="32" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="14" customWidth="1"/>
     <col min="11" max="12" width="10" customWidth="1"/>
     <col min="13" max="13" width="13" customWidth="1"/>
     <col min="14" max="14" width="14" customWidth="1"/>
@@ -499,55 +4334,1062 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" t="s">
+        <v>239</v>
+      </c>
+      <c r="G1" t="s">
+        <v>250</v>
+      </c>
+      <c r="H1" t="s">
+        <v>255</v>
+      </c>
+      <c r="I1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" t="s">
-        <v>9</v>
-      </c>
       <c r="J1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K1" t="s">
-        <v>11</v>
+        <v>240</v>
       </c>
       <c r="L1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="M1" t="s">
-        <v>13</v>
+        <v>245</v>
       </c>
       <c r="N1" t="s">
-        <v>14</v>
+        <v>246</v>
       </c>
       <c r="O1" t="s">
-        <v>15</v>
+        <v>247</v>
       </c>
       <c r="P1" t="s">
-        <v>16</v>
+        <v>248</v>
       </c>
       <c r="Q1" t="s">
-        <v>17</v>
+        <v>249</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" t="s">
+        <v>253</v>
+      </c>
+      <c r="G2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" t="s">
+        <v>257</v>
+      </c>
+      <c r="I2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K2" t="s">
+        <v>253</v>
+      </c>
+      <c r="L2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M2" t="s">
+        <v>253</v>
+      </c>
+      <c r="N2" t="s">
+        <v>253</v>
+      </c>
+      <c r="O2" t="s">
+        <v>253</v>
+      </c>
+      <c r="P2" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" t="s">
+        <v>253</v>
+      </c>
+      <c r="G3" t="s">
+        <v>258</v>
+      </c>
+      <c r="H3" t="s">
+        <v>259</v>
+      </c>
+      <c r="I3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" t="s">
+        <v>253</v>
+      </c>
+      <c r="L3" t="s">
+        <v>48</v>
+      </c>
+      <c r="M3" t="s">
+        <v>253</v>
+      </c>
+      <c r="N3" t="s">
+        <v>253</v>
+      </c>
+      <c r="O3" t="s">
+        <v>253</v>
+      </c>
+      <c r="P3" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>256</v>
+      </c>
+      <c r="B4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4" t="s">
+        <v>253</v>
+      </c>
+      <c r="G4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H4" t="s">
+        <v>253</v>
+      </c>
+      <c r="I4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" t="s">
+        <v>253</v>
+      </c>
+      <c r="L4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M4" t="s">
+        <v>253</v>
+      </c>
+      <c r="N4" t="s">
+        <v>253</v>
+      </c>
+      <c r="O4" t="s">
+        <v>253</v>
+      </c>
+      <c r="P4" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>256</v>
+      </c>
+      <c r="B5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" t="s">
+        <v>253</v>
+      </c>
+      <c r="G5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H5" t="s">
+        <v>253</v>
+      </c>
+      <c r="I5" t="s">
+        <v>62</v>
+      </c>
+      <c r="J5" t="s">
+        <v>33</v>
+      </c>
+      <c r="K5" t="s">
+        <v>253</v>
+      </c>
+      <c r="L5" t="s">
+        <v>48</v>
+      </c>
+      <c r="M5" t="s">
+        <v>253</v>
+      </c>
+      <c r="N5" t="s">
+        <v>253</v>
+      </c>
+      <c r="O5" t="s">
+        <v>253</v>
+      </c>
+      <c r="P5" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>256</v>
+      </c>
+      <c r="B6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F6" t="s">
+        <v>253</v>
+      </c>
+      <c r="G6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H6" t="s">
+        <v>253</v>
+      </c>
+      <c r="I6" t="s">
+        <v>75</v>
+      </c>
+      <c r="J6" t="s">
+        <v>33</v>
+      </c>
+      <c r="K6" t="s">
+        <v>253</v>
+      </c>
+      <c r="L6" t="s">
+        <v>48</v>
+      </c>
+      <c r="M6" t="s">
+        <v>253</v>
+      </c>
+      <c r="N6" t="s">
+        <v>253</v>
+      </c>
+      <c r="O6" t="s">
+        <v>253</v>
+      </c>
+      <c r="P6" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>256</v>
+      </c>
+      <c r="B7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" t="s">
+        <v>87</v>
+      </c>
+      <c r="D7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F7" t="s">
+        <v>253</v>
+      </c>
+      <c r="G7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H7" t="s">
+        <v>253</v>
+      </c>
+      <c r="I7" t="s">
+        <v>86</v>
+      </c>
+      <c r="J7" t="s">
+        <v>33</v>
+      </c>
+      <c r="K7" t="s">
+        <v>253</v>
+      </c>
+      <c r="L7" t="s">
+        <v>48</v>
+      </c>
+      <c r="M7" t="s">
+        <v>253</v>
+      </c>
+      <c r="N7" t="s">
+        <v>253</v>
+      </c>
+      <c r="O7" t="s">
+        <v>253</v>
+      </c>
+      <c r="P7" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>256</v>
+      </c>
+      <c r="B8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" t="s">
+        <v>99</v>
+      </c>
+      <c r="D8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E8" t="s">
+        <v>101</v>
+      </c>
+      <c r="F8" t="s">
+        <v>253</v>
+      </c>
+      <c r="G8" t="s">
+        <v>258</v>
+      </c>
+      <c r="H8" t="s">
+        <v>259</v>
+      </c>
+      <c r="I8" t="s">
+        <v>98</v>
+      </c>
+      <c r="J8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K8" t="s">
+        <v>253</v>
+      </c>
+      <c r="L8" t="s">
+        <v>108</v>
+      </c>
+      <c r="M8" t="s">
+        <v>253</v>
+      </c>
+      <c r="N8" t="s">
+        <v>253</v>
+      </c>
+      <c r="O8" t="s">
+        <v>253</v>
+      </c>
+      <c r="P8" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>256</v>
+      </c>
+      <c r="B9" t="s">
+        <v>109</v>
+      </c>
+      <c r="C9" t="s">
+        <v>111</v>
+      </c>
+      <c r="D9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E9" t="s">
+        <v>113</v>
+      </c>
+      <c r="F9" t="s">
+        <v>253</v>
+      </c>
+      <c r="G9" t="s">
+        <v>258</v>
+      </c>
+      <c r="H9" t="s">
+        <v>259</v>
+      </c>
+      <c r="I9" t="s">
+        <v>110</v>
+      </c>
+      <c r="J9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K9" t="s">
+        <v>253</v>
+      </c>
+      <c r="L9" t="s">
+        <v>119</v>
+      </c>
+      <c r="M9" t="s">
+        <v>253</v>
+      </c>
+      <c r="N9" t="s">
+        <v>253</v>
+      </c>
+      <c r="O9" t="s">
+        <v>253</v>
+      </c>
+      <c r="P9" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>256</v>
+      </c>
+      <c r="B10" t="s">
+        <v>120</v>
+      </c>
+      <c r="C10" t="s">
+        <v>122</v>
+      </c>
+      <c r="D10" t="s">
+        <v>123</v>
+      </c>
+      <c r="E10" t="s">
+        <v>124</v>
+      </c>
+      <c r="F10" t="s">
+        <v>253</v>
+      </c>
+      <c r="G10" t="s">
+        <v>120</v>
+      </c>
+      <c r="H10" t="s">
+        <v>260</v>
+      </c>
+      <c r="I10" t="s">
+        <v>121</v>
+      </c>
+      <c r="J10" t="s">
+        <v>33</v>
+      </c>
+      <c r="K10" t="s">
+        <v>253</v>
+      </c>
+      <c r="L10" t="s">
+        <v>108</v>
+      </c>
+      <c r="M10" t="s">
+        <v>253</v>
+      </c>
+      <c r="N10" t="s">
+        <v>253</v>
+      </c>
+      <c r="O10" t="s">
+        <v>253</v>
+      </c>
+      <c r="P10" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>256</v>
+      </c>
+      <c r="B11" t="s">
+        <v>131</v>
+      </c>
+      <c r="C11" t="s">
+        <v>122</v>
+      </c>
+      <c r="D11" t="s">
+        <v>123</v>
+      </c>
+      <c r="E11" t="s">
+        <v>133</v>
+      </c>
+      <c r="F11" t="s">
+        <v>253</v>
+      </c>
+      <c r="G11" t="s">
+        <v>131</v>
+      </c>
+      <c r="H11" t="s">
+        <v>260</v>
+      </c>
+      <c r="I11" t="s">
+        <v>132</v>
+      </c>
+      <c r="J11" t="s">
+        <v>33</v>
+      </c>
+      <c r="K11" t="s">
+        <v>253</v>
+      </c>
+      <c r="L11" t="s">
+        <v>108</v>
+      </c>
+      <c r="M11" t="s">
+        <v>253</v>
+      </c>
+      <c r="N11" t="s">
+        <v>253</v>
+      </c>
+      <c r="O11" t="s">
+        <v>253</v>
+      </c>
+      <c r="P11" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>256</v>
+      </c>
+      <c r="B12" t="s">
+        <v>138</v>
+      </c>
+      <c r="C12" t="s">
+        <v>140</v>
+      </c>
+      <c r="D12" t="s">
+        <v>123</v>
+      </c>
+      <c r="E12" t="s">
+        <v>143</v>
+      </c>
+      <c r="F12" t="s">
+        <v>253</v>
+      </c>
+      <c r="G12" t="s">
+        <v>258</v>
+      </c>
+      <c r="H12" t="s">
+        <v>259</v>
+      </c>
+      <c r="I12" t="s">
+        <v>139</v>
+      </c>
+      <c r="J12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K12" t="s">
+        <v>253</v>
+      </c>
+      <c r="L12" t="s">
+        <v>108</v>
+      </c>
+      <c r="M12" t="s">
+        <v>253</v>
+      </c>
+      <c r="N12" t="s">
+        <v>253</v>
+      </c>
+      <c r="O12" t="s">
+        <v>253</v>
+      </c>
+      <c r="P12" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>256</v>
+      </c>
+      <c r="B13" t="s">
+        <v>150</v>
+      </c>
+      <c r="C13" t="s">
+        <v>152</v>
+      </c>
+      <c r="D13" t="s">
+        <v>153</v>
+      </c>
+      <c r="E13" t="s">
+        <v>154</v>
+      </c>
+      <c r="F13" t="s">
+        <v>253</v>
+      </c>
+      <c r="G13" t="s">
+        <v>261</v>
+      </c>
+      <c r="H13" t="s">
+        <v>259</v>
+      </c>
+      <c r="I13" t="s">
+        <v>151</v>
+      </c>
+      <c r="J13" t="s">
+        <v>33</v>
+      </c>
+      <c r="K13" t="s">
+        <v>253</v>
+      </c>
+      <c r="L13" t="s">
+        <v>160</v>
+      </c>
+      <c r="M13" t="s">
+        <v>253</v>
+      </c>
+      <c r="N13" t="s">
+        <v>253</v>
+      </c>
+      <c r="O13" t="s">
+        <v>253</v>
+      </c>
+      <c r="P13" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>256</v>
+      </c>
+      <c r="B14" t="s">
+        <v>161</v>
+      </c>
+      <c r="C14" t="s">
+        <v>163</v>
+      </c>
+      <c r="D14" t="s">
+        <v>164</v>
+      </c>
+      <c r="E14" t="s">
+        <v>166</v>
+      </c>
+      <c r="F14" t="s">
+        <v>253</v>
+      </c>
+      <c r="G14" t="s">
+        <v>161</v>
+      </c>
+      <c r="H14" t="s">
+        <v>253</v>
+      </c>
+      <c r="I14" t="s">
+        <v>162</v>
+      </c>
+      <c r="J14" t="s">
+        <v>33</v>
+      </c>
+      <c r="K14" t="s">
+        <v>253</v>
+      </c>
+      <c r="L14" t="s">
+        <v>48</v>
+      </c>
+      <c r="M14" t="s">
+        <v>253</v>
+      </c>
+      <c r="N14" t="s">
+        <v>253</v>
+      </c>
+      <c r="O14" t="s">
+        <v>253</v>
+      </c>
+      <c r="P14" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>256</v>
+      </c>
+      <c r="B15" t="s">
+        <v>172</v>
+      </c>
+      <c r="C15" t="s">
+        <v>174</v>
+      </c>
+      <c r="D15" t="s">
+        <v>175</v>
+      </c>
+      <c r="E15" t="s">
+        <v>176</v>
+      </c>
+      <c r="F15" t="s">
+        <v>253</v>
+      </c>
+      <c r="G15" t="s">
+        <v>261</v>
+      </c>
+      <c r="H15" t="s">
+        <v>259</v>
+      </c>
+      <c r="I15" t="s">
+        <v>173</v>
+      </c>
+      <c r="J15" t="s">
+        <v>33</v>
+      </c>
+      <c r="K15" t="s">
+        <v>253</v>
+      </c>
+      <c r="L15" t="s">
+        <v>182</v>
+      </c>
+      <c r="M15" t="s">
+        <v>253</v>
+      </c>
+      <c r="N15" t="s">
+        <v>253</v>
+      </c>
+      <c r="O15" t="s">
+        <v>253</v>
+      </c>
+      <c r="P15" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>256</v>
+      </c>
+      <c r="B16" t="s">
+        <v>183</v>
+      </c>
+      <c r="C16" t="s">
+        <v>185</v>
+      </c>
+      <c r="D16" t="s">
+        <v>186</v>
+      </c>
+      <c r="E16" t="s">
+        <v>190</v>
+      </c>
+      <c r="F16" t="s">
+        <v>253</v>
+      </c>
+      <c r="G16" t="s">
+        <v>183</v>
+      </c>
+      <c r="H16" t="s">
+        <v>253</v>
+      </c>
+      <c r="I16" t="s">
+        <v>184</v>
+      </c>
+      <c r="J16" t="s">
+        <v>33</v>
+      </c>
+      <c r="K16" t="s">
+        <v>253</v>
+      </c>
+      <c r="L16" t="s">
+        <v>48</v>
+      </c>
+      <c r="M16" t="s">
+        <v>253</v>
+      </c>
+      <c r="N16" t="s">
+        <v>253</v>
+      </c>
+      <c r="O16" t="s">
+        <v>253</v>
+      </c>
+      <c r="P16" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>256</v>
+      </c>
+      <c r="B17" t="s">
+        <v>195</v>
+      </c>
+      <c r="C17" t="s">
+        <v>197</v>
+      </c>
+      <c r="D17" t="s">
+        <v>189</v>
+      </c>
+      <c r="E17" t="s">
+        <v>199</v>
+      </c>
+      <c r="F17" t="s">
+        <v>253</v>
+      </c>
+      <c r="G17" t="s">
+        <v>261</v>
+      </c>
+      <c r="H17" t="s">
+        <v>259</v>
+      </c>
+      <c r="I17" t="s">
+        <v>196</v>
+      </c>
+      <c r="J17" t="s">
+        <v>33</v>
+      </c>
+      <c r="K17" t="s">
+        <v>253</v>
+      </c>
+      <c r="L17" t="s">
+        <v>48</v>
+      </c>
+      <c r="M17" t="s">
+        <v>253</v>
+      </c>
+      <c r="N17" t="s">
+        <v>253</v>
+      </c>
+      <c r="O17" t="s">
+        <v>253</v>
+      </c>
+      <c r="P17" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>256</v>
+      </c>
+      <c r="B18" t="s">
+        <v>205</v>
+      </c>
+      <c r="C18" t="s">
+        <v>207</v>
+      </c>
+      <c r="D18" t="s">
+        <v>189</v>
+      </c>
+      <c r="E18" t="s">
+        <v>208</v>
+      </c>
+      <c r="F18" t="s">
+        <v>253</v>
+      </c>
+      <c r="G18" t="s">
+        <v>205</v>
+      </c>
+      <c r="H18" t="s">
+        <v>262</v>
+      </c>
+      <c r="I18" t="s">
+        <v>206</v>
+      </c>
+      <c r="J18" t="s">
+        <v>33</v>
+      </c>
+      <c r="K18" t="s">
+        <v>253</v>
+      </c>
+      <c r="L18" t="s">
+        <v>48</v>
+      </c>
+      <c r="M18" t="s">
+        <v>253</v>
+      </c>
+      <c r="N18" t="s">
+        <v>253</v>
+      </c>
+      <c r="O18" t="s">
+        <v>253</v>
+      </c>
+      <c r="P18" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>256</v>
+      </c>
+      <c r="B19" t="s">
+        <v>213</v>
+      </c>
+      <c r="C19" t="s">
+        <v>215</v>
+      </c>
+      <c r="D19" t="s">
+        <v>216</v>
+      </c>
+      <c r="E19" t="s">
+        <v>217</v>
+      </c>
+      <c r="F19" t="s">
+        <v>253</v>
+      </c>
+      <c r="G19" t="s">
+        <v>261</v>
+      </c>
+      <c r="H19" t="s">
+        <v>259</v>
+      </c>
+      <c r="I19" t="s">
+        <v>214</v>
+      </c>
+      <c r="J19" t="s">
+        <v>33</v>
+      </c>
+      <c r="K19" t="s">
+        <v>253</v>
+      </c>
+      <c r="L19" t="s">
+        <v>48</v>
+      </c>
+      <c r="M19" t="s">
+        <v>253</v>
+      </c>
+      <c r="N19" t="s">
+        <v>253</v>
+      </c>
+      <c r="O19" t="s">
+        <v>253</v>
+      </c>
+      <c r="P19" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>256</v>
+      </c>
+      <c r="B20" t="s">
+        <v>224</v>
+      </c>
+      <c r="C20" t="s">
+        <v>226</v>
+      </c>
+      <c r="D20" t="s">
+        <v>227</v>
+      </c>
+      <c r="E20" t="s">
+        <v>228</v>
+      </c>
+      <c r="F20" t="s">
+        <v>253</v>
+      </c>
+      <c r="G20" t="s">
+        <v>261</v>
+      </c>
+      <c r="H20" t="s">
+        <v>259</v>
+      </c>
+      <c r="I20" t="s">
+        <v>225</v>
+      </c>
+      <c r="J20" t="s">
+        <v>33</v>
+      </c>
+      <c r="K20" t="s">
+        <v>253</v>
+      </c>
+      <c r="L20" t="s">
+        <v>108</v>
+      </c>
+      <c r="M20" t="s">
+        <v>253</v>
+      </c>
+      <c r="N20" t="s">
+        <v>253</v>
+      </c>
+      <c r="O20" t="s">
+        <v>253</v>
+      </c>
+      <c r="P20" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>253</v>
       </c>
     </row>
   </sheetData>
@@ -558,15 +5400,18 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="7" max="7" width="32" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="14" customWidth="1"/>
     <col min="11" max="12" width="10" customWidth="1"/>
     <col min="13" max="13" width="13" customWidth="1"/>
     <col min="14" max="14" width="14" customWidth="1"/>
@@ -575,55 +5420,1062 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" t="s">
+        <v>239</v>
+      </c>
+      <c r="G1" t="s">
+        <v>250</v>
+      </c>
+      <c r="H1" t="s">
+        <v>255</v>
+      </c>
+      <c r="I1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" t="s">
-        <v>9</v>
-      </c>
       <c r="J1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K1" t="s">
-        <v>11</v>
+        <v>240</v>
       </c>
       <c r="L1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="M1" t="s">
-        <v>13</v>
+        <v>245</v>
       </c>
       <c r="N1" t="s">
-        <v>14</v>
+        <v>246</v>
       </c>
       <c r="O1" t="s">
-        <v>15</v>
+        <v>247</v>
       </c>
       <c r="P1" t="s">
-        <v>16</v>
+        <v>248</v>
       </c>
       <c r="Q1" t="s">
-        <v>17</v>
+        <v>249</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" t="s">
+        <v>253</v>
+      </c>
+      <c r="G2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" t="s">
+        <v>257</v>
+      </c>
+      <c r="I2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K2" t="s">
+        <v>253</v>
+      </c>
+      <c r="L2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M2" t="s">
+        <v>253</v>
+      </c>
+      <c r="N2" t="s">
+        <v>253</v>
+      </c>
+      <c r="O2" t="s">
+        <v>253</v>
+      </c>
+      <c r="P2" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" t="s">
+        <v>253</v>
+      </c>
+      <c r="G3" t="s">
+        <v>258</v>
+      </c>
+      <c r="H3" t="s">
+        <v>259</v>
+      </c>
+      <c r="I3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" t="s">
+        <v>253</v>
+      </c>
+      <c r="L3" t="s">
+        <v>48</v>
+      </c>
+      <c r="M3" t="s">
+        <v>253</v>
+      </c>
+      <c r="N3" t="s">
+        <v>253</v>
+      </c>
+      <c r="O3" t="s">
+        <v>253</v>
+      </c>
+      <c r="P3" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>256</v>
+      </c>
+      <c r="B4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4" t="s">
+        <v>253</v>
+      </c>
+      <c r="G4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H4" t="s">
+        <v>253</v>
+      </c>
+      <c r="I4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" t="s">
+        <v>253</v>
+      </c>
+      <c r="L4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M4" t="s">
+        <v>253</v>
+      </c>
+      <c r="N4" t="s">
+        <v>253</v>
+      </c>
+      <c r="O4" t="s">
+        <v>253</v>
+      </c>
+      <c r="P4" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>256</v>
+      </c>
+      <c r="B5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" t="s">
+        <v>253</v>
+      </c>
+      <c r="G5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H5" t="s">
+        <v>253</v>
+      </c>
+      <c r="I5" t="s">
+        <v>62</v>
+      </c>
+      <c r="J5" t="s">
+        <v>33</v>
+      </c>
+      <c r="K5" t="s">
+        <v>253</v>
+      </c>
+      <c r="L5" t="s">
+        <v>48</v>
+      </c>
+      <c r="M5" t="s">
+        <v>253</v>
+      </c>
+      <c r="N5" t="s">
+        <v>253</v>
+      </c>
+      <c r="O5" t="s">
+        <v>253</v>
+      </c>
+      <c r="P5" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>256</v>
+      </c>
+      <c r="B6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F6" t="s">
+        <v>253</v>
+      </c>
+      <c r="G6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H6" t="s">
+        <v>253</v>
+      </c>
+      <c r="I6" t="s">
+        <v>75</v>
+      </c>
+      <c r="J6" t="s">
+        <v>33</v>
+      </c>
+      <c r="K6" t="s">
+        <v>253</v>
+      </c>
+      <c r="L6" t="s">
+        <v>48</v>
+      </c>
+      <c r="M6" t="s">
+        <v>253</v>
+      </c>
+      <c r="N6" t="s">
+        <v>253</v>
+      </c>
+      <c r="O6" t="s">
+        <v>253</v>
+      </c>
+      <c r="P6" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>256</v>
+      </c>
+      <c r="B7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" t="s">
+        <v>87</v>
+      </c>
+      <c r="D7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F7" t="s">
+        <v>253</v>
+      </c>
+      <c r="G7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H7" t="s">
+        <v>253</v>
+      </c>
+      <c r="I7" t="s">
+        <v>86</v>
+      </c>
+      <c r="J7" t="s">
+        <v>33</v>
+      </c>
+      <c r="K7" t="s">
+        <v>253</v>
+      </c>
+      <c r="L7" t="s">
+        <v>48</v>
+      </c>
+      <c r="M7" t="s">
+        <v>253</v>
+      </c>
+      <c r="N7" t="s">
+        <v>253</v>
+      </c>
+      <c r="O7" t="s">
+        <v>253</v>
+      </c>
+      <c r="P7" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>256</v>
+      </c>
+      <c r="B8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" t="s">
+        <v>99</v>
+      </c>
+      <c r="D8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E8" t="s">
+        <v>101</v>
+      </c>
+      <c r="F8" t="s">
+        <v>253</v>
+      </c>
+      <c r="G8" t="s">
+        <v>258</v>
+      </c>
+      <c r="H8" t="s">
+        <v>259</v>
+      </c>
+      <c r="I8" t="s">
+        <v>98</v>
+      </c>
+      <c r="J8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K8" t="s">
+        <v>253</v>
+      </c>
+      <c r="L8" t="s">
+        <v>108</v>
+      </c>
+      <c r="M8" t="s">
+        <v>253</v>
+      </c>
+      <c r="N8" t="s">
+        <v>253</v>
+      </c>
+      <c r="O8" t="s">
+        <v>253</v>
+      </c>
+      <c r="P8" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>256</v>
+      </c>
+      <c r="B9" t="s">
+        <v>109</v>
+      </c>
+      <c r="C9" t="s">
+        <v>111</v>
+      </c>
+      <c r="D9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E9" t="s">
+        <v>113</v>
+      </c>
+      <c r="F9" t="s">
+        <v>253</v>
+      </c>
+      <c r="G9" t="s">
+        <v>258</v>
+      </c>
+      <c r="H9" t="s">
+        <v>259</v>
+      </c>
+      <c r="I9" t="s">
+        <v>110</v>
+      </c>
+      <c r="J9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K9" t="s">
+        <v>253</v>
+      </c>
+      <c r="L9" t="s">
+        <v>119</v>
+      </c>
+      <c r="M9" t="s">
+        <v>253</v>
+      </c>
+      <c r="N9" t="s">
+        <v>253</v>
+      </c>
+      <c r="O9" t="s">
+        <v>253</v>
+      </c>
+      <c r="P9" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>256</v>
+      </c>
+      <c r="B10" t="s">
+        <v>120</v>
+      </c>
+      <c r="C10" t="s">
+        <v>122</v>
+      </c>
+      <c r="D10" t="s">
+        <v>123</v>
+      </c>
+      <c r="E10" t="s">
+        <v>124</v>
+      </c>
+      <c r="F10" t="s">
+        <v>253</v>
+      </c>
+      <c r="G10" t="s">
+        <v>120</v>
+      </c>
+      <c r="H10" t="s">
+        <v>260</v>
+      </c>
+      <c r="I10" t="s">
+        <v>121</v>
+      </c>
+      <c r="J10" t="s">
+        <v>33</v>
+      </c>
+      <c r="K10" t="s">
+        <v>253</v>
+      </c>
+      <c r="L10" t="s">
+        <v>108</v>
+      </c>
+      <c r="M10" t="s">
+        <v>253</v>
+      </c>
+      <c r="N10" t="s">
+        <v>253</v>
+      </c>
+      <c r="O10" t="s">
+        <v>253</v>
+      </c>
+      <c r="P10" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>256</v>
+      </c>
+      <c r="B11" t="s">
+        <v>131</v>
+      </c>
+      <c r="C11" t="s">
+        <v>122</v>
+      </c>
+      <c r="D11" t="s">
+        <v>123</v>
+      </c>
+      <c r="E11" t="s">
+        <v>133</v>
+      </c>
+      <c r="F11" t="s">
+        <v>253</v>
+      </c>
+      <c r="G11" t="s">
+        <v>131</v>
+      </c>
+      <c r="H11" t="s">
+        <v>260</v>
+      </c>
+      <c r="I11" t="s">
+        <v>132</v>
+      </c>
+      <c r="J11" t="s">
+        <v>33</v>
+      </c>
+      <c r="K11" t="s">
+        <v>253</v>
+      </c>
+      <c r="L11" t="s">
+        <v>108</v>
+      </c>
+      <c r="M11" t="s">
+        <v>253</v>
+      </c>
+      <c r="N11" t="s">
+        <v>253</v>
+      </c>
+      <c r="O11" t="s">
+        <v>253</v>
+      </c>
+      <c r="P11" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>256</v>
+      </c>
+      <c r="B12" t="s">
+        <v>138</v>
+      </c>
+      <c r="C12" t="s">
+        <v>140</v>
+      </c>
+      <c r="D12" t="s">
+        <v>123</v>
+      </c>
+      <c r="E12" t="s">
+        <v>143</v>
+      </c>
+      <c r="F12" t="s">
+        <v>253</v>
+      </c>
+      <c r="G12" t="s">
+        <v>258</v>
+      </c>
+      <c r="H12" t="s">
+        <v>259</v>
+      </c>
+      <c r="I12" t="s">
+        <v>139</v>
+      </c>
+      <c r="J12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K12" t="s">
+        <v>253</v>
+      </c>
+      <c r="L12" t="s">
+        <v>108</v>
+      </c>
+      <c r="M12" t="s">
+        <v>253</v>
+      </c>
+      <c r="N12" t="s">
+        <v>253</v>
+      </c>
+      <c r="O12" t="s">
+        <v>253</v>
+      </c>
+      <c r="P12" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>256</v>
+      </c>
+      <c r="B13" t="s">
+        <v>150</v>
+      </c>
+      <c r="C13" t="s">
+        <v>152</v>
+      </c>
+      <c r="D13" t="s">
+        <v>153</v>
+      </c>
+      <c r="E13" t="s">
+        <v>154</v>
+      </c>
+      <c r="F13" t="s">
+        <v>253</v>
+      </c>
+      <c r="G13" t="s">
+        <v>261</v>
+      </c>
+      <c r="H13" t="s">
+        <v>259</v>
+      </c>
+      <c r="I13" t="s">
+        <v>151</v>
+      </c>
+      <c r="J13" t="s">
+        <v>33</v>
+      </c>
+      <c r="K13" t="s">
+        <v>253</v>
+      </c>
+      <c r="L13" t="s">
+        <v>160</v>
+      </c>
+      <c r="M13" t="s">
+        <v>253</v>
+      </c>
+      <c r="N13" t="s">
+        <v>253</v>
+      </c>
+      <c r="O13" t="s">
+        <v>253</v>
+      </c>
+      <c r="P13" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>256</v>
+      </c>
+      <c r="B14" t="s">
+        <v>161</v>
+      </c>
+      <c r="C14" t="s">
+        <v>163</v>
+      </c>
+      <c r="D14" t="s">
+        <v>164</v>
+      </c>
+      <c r="E14" t="s">
+        <v>166</v>
+      </c>
+      <c r="F14" t="s">
+        <v>253</v>
+      </c>
+      <c r="G14" t="s">
+        <v>161</v>
+      </c>
+      <c r="H14" t="s">
+        <v>253</v>
+      </c>
+      <c r="I14" t="s">
+        <v>162</v>
+      </c>
+      <c r="J14" t="s">
+        <v>33</v>
+      </c>
+      <c r="K14" t="s">
+        <v>253</v>
+      </c>
+      <c r="L14" t="s">
+        <v>48</v>
+      </c>
+      <c r="M14" t="s">
+        <v>253</v>
+      </c>
+      <c r="N14" t="s">
+        <v>253</v>
+      </c>
+      <c r="O14" t="s">
+        <v>253</v>
+      </c>
+      <c r="P14" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>256</v>
+      </c>
+      <c r="B15" t="s">
+        <v>172</v>
+      </c>
+      <c r="C15" t="s">
+        <v>174</v>
+      </c>
+      <c r="D15" t="s">
+        <v>175</v>
+      </c>
+      <c r="E15" t="s">
+        <v>176</v>
+      </c>
+      <c r="F15" t="s">
+        <v>253</v>
+      </c>
+      <c r="G15" t="s">
+        <v>261</v>
+      </c>
+      <c r="H15" t="s">
+        <v>259</v>
+      </c>
+      <c r="I15" t="s">
+        <v>173</v>
+      </c>
+      <c r="J15" t="s">
+        <v>33</v>
+      </c>
+      <c r="K15" t="s">
+        <v>253</v>
+      </c>
+      <c r="L15" t="s">
+        <v>182</v>
+      </c>
+      <c r="M15" t="s">
+        <v>253</v>
+      </c>
+      <c r="N15" t="s">
+        <v>253</v>
+      </c>
+      <c r="O15" t="s">
+        <v>253</v>
+      </c>
+      <c r="P15" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>256</v>
+      </c>
+      <c r="B16" t="s">
+        <v>183</v>
+      </c>
+      <c r="C16" t="s">
+        <v>185</v>
+      </c>
+      <c r="D16" t="s">
+        <v>186</v>
+      </c>
+      <c r="E16" t="s">
+        <v>190</v>
+      </c>
+      <c r="F16" t="s">
+        <v>253</v>
+      </c>
+      <c r="G16" t="s">
+        <v>183</v>
+      </c>
+      <c r="H16" t="s">
+        <v>253</v>
+      </c>
+      <c r="I16" t="s">
+        <v>184</v>
+      </c>
+      <c r="J16" t="s">
+        <v>33</v>
+      </c>
+      <c r="K16" t="s">
+        <v>253</v>
+      </c>
+      <c r="L16" t="s">
+        <v>48</v>
+      </c>
+      <c r="M16" t="s">
+        <v>253</v>
+      </c>
+      <c r="N16" t="s">
+        <v>253</v>
+      </c>
+      <c r="O16" t="s">
+        <v>253</v>
+      </c>
+      <c r="P16" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>256</v>
+      </c>
+      <c r="B17" t="s">
+        <v>195</v>
+      </c>
+      <c r="C17" t="s">
+        <v>197</v>
+      </c>
+      <c r="D17" t="s">
+        <v>189</v>
+      </c>
+      <c r="E17" t="s">
+        <v>199</v>
+      </c>
+      <c r="F17" t="s">
+        <v>253</v>
+      </c>
+      <c r="G17" t="s">
+        <v>261</v>
+      </c>
+      <c r="H17" t="s">
+        <v>259</v>
+      </c>
+      <c r="I17" t="s">
+        <v>196</v>
+      </c>
+      <c r="J17" t="s">
+        <v>33</v>
+      </c>
+      <c r="K17" t="s">
+        <v>253</v>
+      </c>
+      <c r="L17" t="s">
+        <v>48</v>
+      </c>
+      <c r="M17" t="s">
+        <v>253</v>
+      </c>
+      <c r="N17" t="s">
+        <v>253</v>
+      </c>
+      <c r="O17" t="s">
+        <v>253</v>
+      </c>
+      <c r="P17" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>256</v>
+      </c>
+      <c r="B18" t="s">
+        <v>205</v>
+      </c>
+      <c r="C18" t="s">
+        <v>207</v>
+      </c>
+      <c r="D18" t="s">
+        <v>189</v>
+      </c>
+      <c r="E18" t="s">
+        <v>208</v>
+      </c>
+      <c r="F18" t="s">
+        <v>253</v>
+      </c>
+      <c r="G18" t="s">
+        <v>205</v>
+      </c>
+      <c r="H18" t="s">
+        <v>262</v>
+      </c>
+      <c r="I18" t="s">
+        <v>206</v>
+      </c>
+      <c r="J18" t="s">
+        <v>33</v>
+      </c>
+      <c r="K18" t="s">
+        <v>253</v>
+      </c>
+      <c r="L18" t="s">
+        <v>48</v>
+      </c>
+      <c r="M18" t="s">
+        <v>253</v>
+      </c>
+      <c r="N18" t="s">
+        <v>253</v>
+      </c>
+      <c r="O18" t="s">
+        <v>253</v>
+      </c>
+      <c r="P18" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>256</v>
+      </c>
+      <c r="B19" t="s">
+        <v>213</v>
+      </c>
+      <c r="C19" t="s">
+        <v>215</v>
+      </c>
+      <c r="D19" t="s">
+        <v>216</v>
+      </c>
+      <c r="E19" t="s">
+        <v>217</v>
+      </c>
+      <c r="F19" t="s">
+        <v>253</v>
+      </c>
+      <c r="G19" t="s">
+        <v>261</v>
+      </c>
+      <c r="H19" t="s">
+        <v>259</v>
+      </c>
+      <c r="I19" t="s">
+        <v>214</v>
+      </c>
+      <c r="J19" t="s">
+        <v>33</v>
+      </c>
+      <c r="K19" t="s">
+        <v>253</v>
+      </c>
+      <c r="L19" t="s">
+        <v>48</v>
+      </c>
+      <c r="M19" t="s">
+        <v>253</v>
+      </c>
+      <c r="N19" t="s">
+        <v>253</v>
+      </c>
+      <c r="O19" t="s">
+        <v>253</v>
+      </c>
+      <c r="P19" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>256</v>
+      </c>
+      <c r="B20" t="s">
+        <v>224</v>
+      </c>
+      <c r="C20" t="s">
+        <v>226</v>
+      </c>
+      <c r="D20" t="s">
+        <v>227</v>
+      </c>
+      <c r="E20" t="s">
+        <v>228</v>
+      </c>
+      <c r="F20" t="s">
+        <v>253</v>
+      </c>
+      <c r="G20" t="s">
+        <v>261</v>
+      </c>
+      <c r="H20" t="s">
+        <v>259</v>
+      </c>
+      <c r="I20" t="s">
+        <v>225</v>
+      </c>
+      <c r="J20" t="s">
+        <v>33</v>
+      </c>
+      <c r="K20" t="s">
+        <v>253</v>
+      </c>
+      <c r="L20" t="s">
+        <v>108</v>
+      </c>
+      <c r="M20" t="s">
+        <v>253</v>
+      </c>
+      <c r="N20" t="s">
+        <v>253</v>
+      </c>
+      <c r="O20" t="s">
+        <v>253</v>
+      </c>
+      <c r="P20" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>253</v>
       </c>
     </row>
   </sheetData>
